--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125760114</v>
+        <v>125760089</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>98324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>773976</v>
+        <v>773952</v>
       </c>
       <c r="R17" t="n">
-        <v>7176802</v>
+        <v>7176706</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125760084</v>
+        <v>125760114</v>
       </c>
       <c r="B18" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>773979</v>
+        <v>773976</v>
       </c>
       <c r="R18" t="n">
-        <v>7176725</v>
+        <v>7176802</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125760089</v>
+        <v>125760084</v>
       </c>
       <c r="B19" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>773952</v>
+        <v>773979</v>
       </c>
       <c r="R19" t="n">
-        <v>7176706</v>
+        <v>7176725</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125760085</v>
+        <v>125760073</v>
       </c>
       <c r="B29" t="n">
-        <v>80070</v>
+        <v>91513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>774028</v>
+        <v>773962</v>
       </c>
       <c r="R29" t="n">
-        <v>7176813</v>
+        <v>7176754</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125760073</v>
+        <v>125760085</v>
       </c>
       <c r="B30" t="n">
-        <v>91513</v>
+        <v>80070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>773962</v>
+        <v>774028</v>
       </c>
       <c r="R30" t="n">
-        <v>7176754</v>
+        <v>7176813</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4269,32 +4269,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125760077</v>
+        <v>125760091</v>
       </c>
       <c r="B39" t="n">
-        <v>91513</v>
+        <v>98324</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>773963</v>
+        <v>773895</v>
       </c>
       <c r="R39" t="n">
-        <v>7176727</v>
+        <v>7176617</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125760091</v>
+        <v>125760077</v>
       </c>
       <c r="B40" t="n">
-        <v>98324</v>
+        <v>91513</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>773895</v>
+        <v>773963</v>
       </c>
       <c r="R40" t="n">
-        <v>7176617</v>
+        <v>7176727</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125760115</v>
+        <v>125760052</v>
       </c>
       <c r="B55" t="n">
-        <v>57651</v>
+        <v>91220</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>774095</v>
+        <v>774143</v>
       </c>
       <c r="R55" t="n">
-        <v>7176826</v>
+        <v>7176723</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5913,11 +5913,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5944,10 +5939,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125760052</v>
+        <v>125760115</v>
       </c>
       <c r="B56" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5955,21 +5950,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5979,10 +5974,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>774143</v>
+        <v>774095</v>
       </c>
       <c r="R56" t="n">
-        <v>7176723</v>
+        <v>7176826</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6015,6 +6010,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6041,10 +6041,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125760097</v>
+        <v>125760086</v>
       </c>
       <c r="B57" t="n">
-        <v>98324</v>
+        <v>91418</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6052,34 +6052,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>774142</v>
+        <v>774175</v>
       </c>
       <c r="R57" t="n">
-        <v>7176720</v>
+        <v>7176775</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6120,6 +6123,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6138,38 +6142,35 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125760086</v>
+        <v>125760076</v>
       </c>
       <c r="B58" t="n">
-        <v>91418</v>
+        <v>91513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
@@ -6220,7 +6221,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760076</v>
+        <v>125760061</v>
       </c>
       <c r="B59" t="n">
-        <v>91513</v>
+        <v>57811</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>774175</v>
+        <v>774115</v>
       </c>
       <c r="R59" t="n">
-        <v>7176775</v>
+        <v>7176821</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,32 +6336,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125760061</v>
+        <v>125760097</v>
       </c>
       <c r="B60" t="n">
-        <v>57811</v>
+        <v>98324</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>774115</v>
+        <v>774142</v>
       </c>
       <c r="R60" t="n">
-        <v>7176821</v>
+        <v>7176720</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125760088</v>
       </c>
       <c r="B2" t="n">
-        <v>91804</v>
+        <v>91811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125760051</v>
       </c>
       <c r="B3" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>125760092</v>
       </c>
       <c r="B6" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>125760093</v>
       </c>
       <c r="B7" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760090</v>
+        <v>125760071</v>
       </c>
       <c r="B9" t="n">
-        <v>98324</v>
+        <v>91678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>773892</v>
+        <v>774022</v>
       </c>
       <c r="R9" t="n">
-        <v>7176629</v>
+        <v>7176810</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760094</v>
+        <v>125760090</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774050</v>
+        <v>773892</v>
       </c>
       <c r="R10" t="n">
-        <v>7176592</v>
+        <v>7176629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760071</v>
+        <v>125760094</v>
       </c>
       <c r="B11" t="n">
-        <v>91671</v>
+        <v>98331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774022</v>
+        <v>774050</v>
       </c>
       <c r="R11" t="n">
-        <v>7176810</v>
+        <v>7176592</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125760056</v>
+        <v>125760119</v>
       </c>
       <c r="B12" t="n">
-        <v>91220</v>
+        <v>80105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>773968</v>
+        <v>773979</v>
       </c>
       <c r="R12" t="n">
-        <v>7176780</v>
+        <v>7176725</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760119</v>
+        <v>125760056</v>
       </c>
       <c r="B13" t="n">
-        <v>80105</v>
+        <v>91227</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>773979</v>
+        <v>773968</v>
       </c>
       <c r="R13" t="n">
-        <v>7176725</v>
+        <v>7176780</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>125760106</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125760089</v>
+        <v>125760114</v>
       </c>
       <c r="B17" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>773952</v>
+        <v>773976</v>
       </c>
       <c r="R17" t="n">
-        <v>7176706</v>
+        <v>7176802</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125760114</v>
+        <v>125760084</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>773976</v>
+        <v>773979</v>
       </c>
       <c r="R18" t="n">
-        <v>7176802</v>
+        <v>7176725</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125760084</v>
+        <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>773979</v>
+        <v>773952</v>
       </c>
       <c r="R19" t="n">
-        <v>7176725</v>
+        <v>7176706</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
         <v>125760058</v>
       </c>
       <c r="B20" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125760066</v>
+        <v>125760082</v>
       </c>
       <c r="B22" t="n">
-        <v>91170</v>
+        <v>80070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>774006</v>
+        <v>773931</v>
       </c>
       <c r="R22" t="n">
-        <v>7176718</v>
+        <v>7176699</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125760057</v>
+        <v>125760110</v>
       </c>
       <c r="B23" t="n">
-        <v>91220</v>
+        <v>78967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>774006</v>
+        <v>774041</v>
       </c>
       <c r="R23" t="n">
-        <v>7176806</v>
+        <v>7176829</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125760110</v>
+        <v>125760066</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>91177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>774041</v>
+        <v>774006</v>
       </c>
       <c r="R24" t="n">
-        <v>7176829</v>
+        <v>7176718</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125760082</v>
+        <v>125760057</v>
       </c>
       <c r="B25" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>773931</v>
+        <v>774006</v>
       </c>
       <c r="R25" t="n">
-        <v>7176699</v>
+        <v>7176806</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125760045</v>
+        <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>78999</v>
+        <v>91921</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>773995</v>
+        <v>774009</v>
       </c>
       <c r="R27" t="n">
-        <v>7176808</v>
+        <v>7176814</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125760059</v>
+        <v>125760045</v>
       </c>
       <c r="B28" t="n">
-        <v>91914</v>
+        <v>78999</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>774009</v>
+        <v>773995</v>
       </c>
       <c r="R28" t="n">
-        <v>7176814</v>
+        <v>7176808</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3302,7 +3302,7 @@
         <v>125760073</v>
       </c>
       <c r="B29" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>125760067</v>
       </c>
       <c r="B31" t="n">
-        <v>91170</v>
+        <v>91177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>125760050</v>
       </c>
       <c r="B32" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125760044</v>
+        <v>125760048</v>
       </c>
       <c r="B33" t="n">
-        <v>78999</v>
+        <v>91192</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>774005</v>
+        <v>774008</v>
       </c>
       <c r="R33" t="n">
-        <v>7176711</v>
+        <v>7176756</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125760055</v>
+        <v>125760044</v>
       </c>
       <c r="B34" t="n">
-        <v>91220</v>
+        <v>78999</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>773997</v>
+        <v>774005</v>
       </c>
       <c r="R34" t="n">
-        <v>7176755</v>
+        <v>7176711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3881,32 +3881,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125760048</v>
+        <v>125760055</v>
       </c>
       <c r="B35" t="n">
-        <v>91185</v>
+        <v>91227</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>774008</v>
+        <v>773997</v>
       </c>
       <c r="R35" t="n">
-        <v>7176756</v>
+        <v>7176755</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125760049</v>
+        <v>125760113</v>
       </c>
       <c r="B36" t="n">
-        <v>91575</v>
+        <v>78967</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>773997</v>
+        <v>774009</v>
       </c>
       <c r="R36" t="n">
-        <v>7176755</v>
+        <v>7176817</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125760113</v>
+        <v>125760049</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>91582</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>774009</v>
+        <v>773997</v>
       </c>
       <c r="R37" t="n">
-        <v>7176817</v>
+        <v>7176755</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4175,7 +4175,7 @@
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,32 +4269,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125760091</v>
+        <v>125760077</v>
       </c>
       <c r="B39" t="n">
-        <v>98324</v>
+        <v>91520</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>773895</v>
+        <v>773963</v>
       </c>
       <c r="R39" t="n">
-        <v>7176617</v>
+        <v>7176727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125760077</v>
+        <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>91513</v>
+        <v>98331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>773963</v>
+        <v>773895</v>
       </c>
       <c r="R40" t="n">
-        <v>7176727</v>
+        <v>7176617</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>125760105</v>
       </c>
       <c r="B43" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125760118</v>
+        <v>125760117</v>
       </c>
       <c r="B46" t="n">
-        <v>88626</v>
+        <v>78967</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4972,34 +4972,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>774109</v>
+        <v>774183</v>
       </c>
       <c r="R46" t="n">
-        <v>7176799</v>
+        <v>7176785</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5040,6 +5047,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5058,10 +5066,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125760117</v>
+        <v>125760118</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>88633</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5069,41 +5077,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>774183</v>
+        <v>774109</v>
       </c>
       <c r="R47" t="n">
-        <v>7176785</v>
+        <v>7176799</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5144,7 +5145,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760095</v>
+        <v>125760096</v>
       </c>
       <c r="B48" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774109</v>
+        <v>774131</v>
       </c>
       <c r="R48" t="n">
-        <v>7176695</v>
+        <v>7176720</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,32 +5260,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760100</v>
+        <v>125760116</v>
       </c>
       <c r="B49" t="n">
-        <v>98324</v>
+        <v>98248</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774165</v>
+        <v>774119</v>
       </c>
       <c r="R49" t="n">
-        <v>7176738</v>
+        <v>7176822</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,32 +5357,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760116</v>
+        <v>125760095</v>
       </c>
       <c r="B50" t="n">
-        <v>98241</v>
+        <v>98331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774119</v>
+        <v>774109</v>
       </c>
       <c r="R50" t="n">
-        <v>7176822</v>
+        <v>7176695</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,10 +5454,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760096</v>
+        <v>125760100</v>
       </c>
       <c r="B51" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774131</v>
+        <v>774165</v>
       </c>
       <c r="R51" t="n">
-        <v>7176720</v>
+        <v>7176738</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5554,7 +5554,7 @@
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125760052</v>
+        <v>125760115</v>
       </c>
       <c r="B55" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>774143</v>
+        <v>774095</v>
       </c>
       <c r="R55" t="n">
-        <v>7176723</v>
+        <v>7176826</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5913,6 +5913,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5939,10 +5944,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125760115</v>
+        <v>125760052</v>
       </c>
       <c r="B56" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5950,21 +5955,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5974,10 +5979,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>774095</v>
+        <v>774143</v>
       </c>
       <c r="R56" t="n">
-        <v>7176826</v>
+        <v>7176723</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6010,11 +6015,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6044,7 +6044,7 @@
         <v>125760086</v>
       </c>
       <c r="B57" t="n">
-        <v>91418</v>
+        <v>91425</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>125760076</v>
       </c>
       <c r="B58" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>125760097</v>
       </c>
       <c r="B60" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>125760072</v>
       </c>
       <c r="B62" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>125760053</v>
       </c>
       <c r="B65" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>125760074</v>
       </c>
       <c r="B66" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7016,32 +7016,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125760109</v>
+        <v>125760103</v>
       </c>
       <c r="B67" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>774182</v>
+        <v>774172</v>
       </c>
       <c r="R67" t="n">
-        <v>7176808</v>
+        <v>7176751</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125760103</v>
+        <v>125760109</v>
       </c>
       <c r="B68" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>774172</v>
+        <v>774182</v>
       </c>
       <c r="R68" t="n">
-        <v>7176751</v>
+        <v>7176808</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91624</v>
+        <v>91631</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125760058</v>
+        <v>125760081</v>
       </c>
       <c r="B20" t="n">
-        <v>91227</v>
+        <v>80098</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>774022</v>
+        <v>773937</v>
       </c>
       <c r="R20" t="n">
-        <v>7176810</v>
+        <v>7176636</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125760081</v>
+        <v>125760058</v>
       </c>
       <c r="B21" t="n">
-        <v>80098</v>
+        <v>91227</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>773937</v>
+        <v>774022</v>
       </c>
       <c r="R21" t="n">
-        <v>7176636</v>
+        <v>7176810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125760073</v>
+        <v>125760085</v>
       </c>
       <c r="B29" t="n">
-        <v>91520</v>
+        <v>80070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>773962</v>
+        <v>774028</v>
       </c>
       <c r="R29" t="n">
-        <v>7176754</v>
+        <v>7176813</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125760085</v>
+        <v>125760073</v>
       </c>
       <c r="B30" t="n">
-        <v>80070</v>
+        <v>91520</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>774028</v>
+        <v>773962</v>
       </c>
       <c r="R30" t="n">
-        <v>7176813</v>
+        <v>7176754</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125760115</v>
+        <v>125760052</v>
       </c>
       <c r="B55" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>774095</v>
+        <v>774143</v>
       </c>
       <c r="R55" t="n">
-        <v>7176826</v>
+        <v>7176723</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5913,11 +5913,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5944,10 +5939,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125760052</v>
+        <v>125760115</v>
       </c>
       <c r="B56" t="n">
-        <v>91227</v>
+        <v>57651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5955,21 +5950,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5979,10 +5974,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>774143</v>
+        <v>774095</v>
       </c>
       <c r="R56" t="n">
-        <v>7176723</v>
+        <v>7176826</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6015,6 +6010,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125760088</v>
+        <v>125760112</v>
       </c>
       <c r="B2" t="n">
-        <v>91811</v>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774000</v>
+        <v>774025</v>
       </c>
       <c r="R2" t="n">
-        <v>7176753</v>
+        <v>7176810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125760051</v>
+        <v>125760083</v>
       </c>
       <c r="B3" t="n">
-        <v>91227</v>
+        <v>80070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>773924</v>
+        <v>774042</v>
       </c>
       <c r="R3" t="n">
-        <v>7176602</v>
+        <v>7176609</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,45 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125760112</v>
+        <v>125760088</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>91811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774025</v>
+        <v>774000</v>
       </c>
       <c r="R4" t="n">
-        <v>7176810</v>
+        <v>7176753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125760083</v>
+        <v>125760051</v>
       </c>
       <c r="B5" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774042</v>
+        <v>773924</v>
       </c>
       <c r="R5" t="n">
-        <v>7176609</v>
+        <v>7176602</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125760092</v>
+        <v>125760046</v>
       </c>
       <c r="B6" t="n">
-        <v>98331</v>
+        <v>78999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>773927</v>
+        <v>773999</v>
       </c>
       <c r="R6" t="n">
-        <v>7176601</v>
+        <v>7176749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,6 +1146,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1164,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125760093</v>
+        <v>125760092</v>
       </c>
       <c r="B7" t="n">
         <v>98331</v>
@@ -1199,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>773964</v>
+        <v>773927</v>
       </c>
       <c r="R7" t="n">
-        <v>7176602</v>
+        <v>7176601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125760046</v>
+        <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>773999</v>
+        <v>773964</v>
       </c>
       <c r="R8" t="n">
-        <v>7176749</v>
+        <v>7176602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1340,7 +1341,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125760119</v>
+        <v>125760069</v>
       </c>
       <c r="B12" t="n">
-        <v>80105</v>
+        <v>57648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>773979</v>
+        <v>774048</v>
       </c>
       <c r="R12" t="n">
-        <v>7176725</v>
+        <v>7176608</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760056</v>
+        <v>125760070</v>
       </c>
       <c r="B13" t="n">
-        <v>91227</v>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>773968</v>
+        <v>774000</v>
       </c>
       <c r="R13" t="n">
-        <v>7176780</v>
+        <v>7176761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125760069</v>
+        <v>125760106</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>98331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>774048</v>
+        <v>773963</v>
       </c>
       <c r="R14" t="n">
-        <v>7176608</v>
+        <v>7176727</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125760070</v>
+        <v>125760119</v>
       </c>
       <c r="B15" t="n">
-        <v>57648</v>
+        <v>80105</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774000</v>
+        <v>773979</v>
       </c>
       <c r="R15" t="n">
-        <v>7176761</v>
+        <v>7176725</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125760106</v>
+        <v>125760056</v>
       </c>
       <c r="B16" t="n">
-        <v>98331</v>
+        <v>91227</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>773963</v>
+        <v>773968</v>
       </c>
       <c r="R16" t="n">
-        <v>7176727</v>
+        <v>7176780</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125760085</v>
+        <v>125760073</v>
       </c>
       <c r="B29" t="n">
-        <v>80070</v>
+        <v>91520</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>774028</v>
+        <v>773962</v>
       </c>
       <c r="R29" t="n">
-        <v>7176813</v>
+        <v>7176754</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125760073</v>
+        <v>125760085</v>
       </c>
       <c r="B30" t="n">
-        <v>91520</v>
+        <v>80070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>773962</v>
+        <v>774028</v>
       </c>
       <c r="R30" t="n">
-        <v>7176754</v>
+        <v>7176813</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760096</v>
+        <v>125760095</v>
       </c>
       <c r="B48" t="n">
         <v>98331</v>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774131</v>
+        <v>774109</v>
       </c>
       <c r="R48" t="n">
-        <v>7176720</v>
+        <v>7176695</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,32 +5260,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760116</v>
+        <v>125760100</v>
       </c>
       <c r="B49" t="n">
-        <v>98248</v>
+        <v>98331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774119</v>
+        <v>774165</v>
       </c>
       <c r="R49" t="n">
-        <v>7176822</v>
+        <v>7176738</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,7 +5357,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760095</v>
+        <v>125760096</v>
       </c>
       <c r="B50" t="n">
         <v>98331</v>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774109</v>
+        <v>774131</v>
       </c>
       <c r="R50" t="n">
-        <v>7176695</v>
+        <v>7176720</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760100</v>
+        <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98331</v>
+        <v>98248</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774165</v>
+        <v>774119</v>
       </c>
       <c r="R51" t="n">
-        <v>7176738</v>
+        <v>7176822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125760062</v>
+        <v>125760099</v>
       </c>
       <c r="B53" t="n">
-        <v>57811</v>
+        <v>98331</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>774110</v>
+        <v>774146</v>
       </c>
       <c r="R53" t="n">
-        <v>7176824</v>
+        <v>7176735</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,32 +5745,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125760099</v>
+        <v>125760062</v>
       </c>
       <c r="B54" t="n">
-        <v>98331</v>
+        <v>57811</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>774146</v>
+        <v>774110</v>
       </c>
       <c r="R54" t="n">
-        <v>7176735</v>
+        <v>7176824</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125760072</v>
+        <v>125760108</v>
       </c>
       <c r="B62" t="n">
-        <v>91520</v>
+        <v>78967</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>774185</v>
+        <v>774201</v>
       </c>
       <c r="R62" t="n">
-        <v>7176787</v>
+        <v>7176809</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6609,7 +6609,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6628,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125760108</v>
+        <v>125760072</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>91520</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6639,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6663,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>774201</v>
+        <v>774185</v>
       </c>
       <c r="R63" t="n">
-        <v>7176809</v>
+        <v>7176787</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,6 +6706,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91631</v>
+        <v>91632</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125760112</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125760083</v>
       </c>
       <c r="B3" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125760088</v>
       </c>
       <c r="B4" t="n">
-        <v>91811</v>
+        <v>91815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>125760051</v>
       </c>
       <c r="B5" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>125760046</v>
       </c>
       <c r="B6" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125760092</v>
+        <v>125760093</v>
       </c>
       <c r="B7" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>773927</v>
+        <v>773964</v>
       </c>
       <c r="R7" t="n">
-        <v>7176601</v>
+        <v>7176602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125760093</v>
+        <v>125760092</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>773964</v>
+        <v>773927</v>
       </c>
       <c r="R8" t="n">
-        <v>7176602</v>
+        <v>7176601</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760071</v>
+        <v>125760090</v>
       </c>
       <c r="B9" t="n">
-        <v>91678</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774022</v>
+        <v>773892</v>
       </c>
       <c r="R9" t="n">
-        <v>7176810</v>
+        <v>7176629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760090</v>
+        <v>125760094</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>773892</v>
+        <v>774050</v>
       </c>
       <c r="R10" t="n">
-        <v>7176629</v>
+        <v>7176592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760094</v>
+        <v>125760071</v>
       </c>
       <c r="B11" t="n">
-        <v>98331</v>
+        <v>91682</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774050</v>
+        <v>774022</v>
       </c>
       <c r="R11" t="n">
-        <v>7176592</v>
+        <v>7176810</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125760069</v>
+        <v>125760106</v>
       </c>
       <c r="B12" t="n">
-        <v>57648</v>
+        <v>98334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>774048</v>
+        <v>773963</v>
       </c>
       <c r="R12" t="n">
-        <v>7176608</v>
+        <v>7176727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760070</v>
+        <v>125760119</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>80106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>774000</v>
+        <v>773979</v>
       </c>
       <c r="R13" t="n">
-        <v>7176761</v>
+        <v>7176725</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125760106</v>
+        <v>125760069</v>
       </c>
       <c r="B14" t="n">
-        <v>98331</v>
+        <v>57648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>773963</v>
+        <v>774048</v>
       </c>
       <c r="R14" t="n">
-        <v>7176727</v>
+        <v>7176608</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125760119</v>
+        <v>125760070</v>
       </c>
       <c r="B15" t="n">
-        <v>80105</v>
+        <v>57648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>773979</v>
+        <v>774000</v>
       </c>
       <c r="R15" t="n">
-        <v>7176725</v>
+        <v>7176761</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>125760056</v>
       </c>
       <c r="B16" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125760114</v>
+        <v>125760089</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>773976</v>
+        <v>773952</v>
       </c>
       <c r="R17" t="n">
-        <v>7176802</v>
+        <v>7176706</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125760084</v>
+        <v>125760114</v>
       </c>
       <c r="B18" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>773979</v>
+        <v>773976</v>
       </c>
       <c r="R18" t="n">
-        <v>7176725</v>
+        <v>7176802</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125760089</v>
+        <v>125760084</v>
       </c>
       <c r="B19" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>773952</v>
+        <v>773979</v>
       </c>
       <c r="R19" t="n">
-        <v>7176706</v>
+        <v>7176725</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
         <v>125760081</v>
       </c>
       <c r="B20" t="n">
-        <v>80098</v>
+        <v>80099</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>125760058</v>
       </c>
       <c r="B21" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125760082</v>
+        <v>125760110</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>773931</v>
+        <v>774041</v>
       </c>
       <c r="R22" t="n">
-        <v>7176699</v>
+        <v>7176829</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125760110</v>
+        <v>125760082</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>774041</v>
+        <v>773931</v>
       </c>
       <c r="R23" t="n">
-        <v>7176829</v>
+        <v>7176699</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
         <v>125760066</v>
       </c>
       <c r="B24" t="n">
-        <v>91177</v>
+        <v>91178</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>125760057</v>
       </c>
       <c r="B25" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>125760111</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>91921</v>
+        <v>91925</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>125760045</v>
       </c>
       <c r="B28" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125760073</v>
+        <v>125760085</v>
       </c>
       <c r="B29" t="n">
-        <v>91520</v>
+        <v>80071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>773962</v>
+        <v>774028</v>
       </c>
       <c r="R29" t="n">
-        <v>7176754</v>
+        <v>7176813</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125760085</v>
+        <v>125760073</v>
       </c>
       <c r="B30" t="n">
-        <v>80070</v>
+        <v>91524</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>774028</v>
+        <v>773962</v>
       </c>
       <c r="R30" t="n">
-        <v>7176813</v>
+        <v>7176754</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3496,7 +3496,7 @@
         <v>125760067</v>
       </c>
       <c r="B31" t="n">
-        <v>91177</v>
+        <v>91178</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>125760050</v>
       </c>
       <c r="B32" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>125760048</v>
       </c>
       <c r="B33" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>125760044</v>
       </c>
       <c r="B34" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>125760055</v>
       </c>
       <c r="B35" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125760113</v>
+        <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>91586</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>774009</v>
+        <v>773997</v>
       </c>
       <c r="R36" t="n">
-        <v>7176817</v>
+        <v>7176755</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125760049</v>
+        <v>125760113</v>
       </c>
       <c r="B37" t="n">
-        <v>91582</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>773997</v>
+        <v>774009</v>
       </c>
       <c r="R37" t="n">
-        <v>7176755</v>
+        <v>7176817</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4175,7 +4175,7 @@
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,32 +4269,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125760077</v>
+        <v>125760091</v>
       </c>
       <c r="B39" t="n">
-        <v>91520</v>
+        <v>98334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>773963</v>
+        <v>773895</v>
       </c>
       <c r="R39" t="n">
-        <v>7176727</v>
+        <v>7176617</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125760091</v>
+        <v>125760077</v>
       </c>
       <c r="B40" t="n">
-        <v>98331</v>
+        <v>91524</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>773895</v>
+        <v>773963</v>
       </c>
       <c r="R40" t="n">
-        <v>7176617</v>
+        <v>7176727</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>125760105</v>
       </c>
       <c r="B43" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>125760065</v>
       </c>
       <c r="B44" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125760117</v>
+        <v>125760118</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>88637</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4972,41 +4972,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>774183</v>
+        <v>774109</v>
       </c>
       <c r="R46" t="n">
-        <v>7176785</v>
+        <v>7176799</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5047,7 +5040,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5066,10 +5058,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125760118</v>
+        <v>125760117</v>
       </c>
       <c r="B47" t="n">
-        <v>88633</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5077,34 +5069,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>774109</v>
+        <v>774183</v>
       </c>
       <c r="R47" t="n">
-        <v>7176799</v>
+        <v>7176785</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5145,6 +5144,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760095</v>
+        <v>125760116</v>
       </c>
       <c r="B48" t="n">
-        <v>98331</v>
+        <v>98251</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774109</v>
+        <v>774119</v>
       </c>
       <c r="R48" t="n">
-        <v>7176695</v>
+        <v>7176822</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760100</v>
+        <v>125760095</v>
       </c>
       <c r="B49" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774165</v>
+        <v>774109</v>
       </c>
       <c r="R49" t="n">
-        <v>7176738</v>
+        <v>7176695</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,10 +5357,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760096</v>
+        <v>125760100</v>
       </c>
       <c r="B50" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774131</v>
+        <v>774165</v>
       </c>
       <c r="R50" t="n">
-        <v>7176720</v>
+        <v>7176738</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760116</v>
+        <v>125760096</v>
       </c>
       <c r="B51" t="n">
-        <v>98248</v>
+        <v>98334</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774119</v>
+        <v>774131</v>
       </c>
       <c r="R51" t="n">
-        <v>7176822</v>
+        <v>7176720</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5554,7 +5554,7 @@
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>125760099</v>
       </c>
       <c r="B53" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>125760052</v>
       </c>
       <c r="B55" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6041,10 +6041,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125760086</v>
+        <v>125760097</v>
       </c>
       <c r="B57" t="n">
-        <v>91425</v>
+        <v>98334</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6052,37 +6052,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>774175</v>
+        <v>774142</v>
       </c>
       <c r="R57" t="n">
-        <v>7176775</v>
+        <v>7176720</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6123,7 +6120,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6142,35 +6138,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125760076</v>
+        <v>125760086</v>
       </c>
       <c r="B58" t="n">
-        <v>91520</v>
+        <v>91429</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
@@ -6221,6 +6220,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760061</v>
+        <v>125760076</v>
       </c>
       <c r="B59" t="n">
-        <v>57811</v>
+        <v>91524</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>774115</v>
+        <v>774175</v>
       </c>
       <c r="R59" t="n">
-        <v>7176821</v>
+        <v>7176775</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,32 +6336,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125760097</v>
+        <v>125760061</v>
       </c>
       <c r="B60" t="n">
-        <v>98331</v>
+        <v>57811</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>774142</v>
+        <v>774115</v>
       </c>
       <c r="R60" t="n">
-        <v>7176720</v>
+        <v>7176821</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6436,7 +6436,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125760108</v>
+        <v>125760063</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>57811</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>774201</v>
+        <v>774078</v>
       </c>
       <c r="R62" t="n">
-        <v>7176809</v>
+        <v>7176829</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125760072</v>
+        <v>125760108</v>
       </c>
       <c r="B63" t="n">
-        <v>91520</v>
+        <v>78968</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>774185</v>
+        <v>774201</v>
       </c>
       <c r="R63" t="n">
-        <v>7176787</v>
+        <v>7176809</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6706,7 +6706,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6725,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125760063</v>
+        <v>125760072</v>
       </c>
       <c r="B64" t="n">
-        <v>57811</v>
+        <v>91524</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6736,21 +6735,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6760,10 +6759,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>774078</v>
+        <v>774185</v>
       </c>
       <c r="R64" t="n">
-        <v>7176829</v>
+        <v>7176787</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,6 +6803,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>125760053</v>
       </c>
       <c r="B65" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>125760074</v>
       </c>
       <c r="B66" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7016,32 +7016,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125760103</v>
+        <v>125760109</v>
       </c>
       <c r="B67" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>774172</v>
+        <v>774182</v>
       </c>
       <c r="R67" t="n">
-        <v>7176751</v>
+        <v>7176808</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125760109</v>
+        <v>125760103</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>774182</v>
+        <v>774172</v>
       </c>
       <c r="R68" t="n">
-        <v>7176808</v>
+        <v>7176751</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91632</v>
+        <v>91635</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125760112</v>
+        <v>125760088</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>91815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774025</v>
+        <v>774000</v>
       </c>
       <c r="R2" t="n">
-        <v>7176810</v>
+        <v>7176753</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125760083</v>
+        <v>125760051</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>91228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774042</v>
+        <v>773924</v>
       </c>
       <c r="R3" t="n">
-        <v>7176609</v>
+        <v>7176602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,48 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125760088</v>
+        <v>125760112</v>
       </c>
       <c r="B4" t="n">
-        <v>91815</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774000</v>
+        <v>774025</v>
       </c>
       <c r="R4" t="n">
-        <v>7176753</v>
+        <v>7176810</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125760051</v>
+        <v>125760083</v>
       </c>
       <c r="B5" t="n">
-        <v>91228</v>
+        <v>80071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>773924</v>
+        <v>774042</v>
       </c>
       <c r="R5" t="n">
-        <v>7176602</v>
+        <v>7176609</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760090</v>
+        <v>125760094</v>
       </c>
       <c r="B9" t="n">
         <v>98334</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>773892</v>
+        <v>774050</v>
       </c>
       <c r="R9" t="n">
-        <v>7176629</v>
+        <v>7176592</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760094</v>
+        <v>125760071</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>91682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774050</v>
+        <v>774022</v>
       </c>
       <c r="R10" t="n">
-        <v>7176592</v>
+        <v>7176810</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760071</v>
+        <v>125760090</v>
       </c>
       <c r="B11" t="n">
-        <v>91682</v>
+        <v>98334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774022</v>
+        <v>773892</v>
       </c>
       <c r="R11" t="n">
-        <v>7176810</v>
+        <v>7176629</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125760118</v>
+        <v>125760117</v>
       </c>
       <c r="B46" t="n">
-        <v>88637</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4972,34 +4972,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>774109</v>
+        <v>774183</v>
       </c>
       <c r="R46" t="n">
-        <v>7176799</v>
+        <v>7176785</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5040,6 +5047,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5058,10 +5066,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125760117</v>
+        <v>125760118</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>88637</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5069,41 +5077,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>774183</v>
+        <v>774109</v>
       </c>
       <c r="R47" t="n">
-        <v>7176785</v>
+        <v>7176799</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5144,7 +5145,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125760063</v>
+        <v>125760108</v>
       </c>
       <c r="B62" t="n">
-        <v>57811</v>
+        <v>78968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>774078</v>
+        <v>774201</v>
       </c>
       <c r="R62" t="n">
-        <v>7176829</v>
+        <v>7176809</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125760108</v>
+        <v>125760072</v>
       </c>
       <c r="B63" t="n">
-        <v>78968</v>
+        <v>91524</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>774201</v>
+        <v>774185</v>
       </c>
       <c r="R63" t="n">
-        <v>7176809</v>
+        <v>7176787</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6706,6 +6706,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6724,10 +6725,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125760072</v>
+        <v>125760063</v>
       </c>
       <c r="B64" t="n">
-        <v>91524</v>
+        <v>57811</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6735,21 +6736,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6759,10 +6760,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>774185</v>
+        <v>774078</v>
       </c>
       <c r="R64" t="n">
-        <v>7176787</v>
+        <v>7176829</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6803,7 +6804,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125760088</v>
+        <v>125760083</v>
       </c>
       <c r="B2" t="n">
-        <v>91815</v>
+        <v>80075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1179</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774000</v>
+        <v>774042</v>
       </c>
       <c r="R2" t="n">
-        <v>7176753</v>
+        <v>7176609</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,45 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125760051</v>
+        <v>125760088</v>
       </c>
       <c r="B3" t="n">
-        <v>91228</v>
+        <v>91819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>773924</v>
+        <v>774000</v>
       </c>
       <c r="R3" t="n">
-        <v>7176602</v>
+        <v>7176753</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125760112</v>
+        <v>125760051</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>91232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774025</v>
+        <v>773924</v>
       </c>
       <c r="R4" t="n">
-        <v>7176810</v>
+        <v>7176602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125760083</v>
+        <v>125760112</v>
       </c>
       <c r="B5" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774042</v>
+        <v>774025</v>
       </c>
       <c r="R5" t="n">
-        <v>7176609</v>
+        <v>7176810</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,7 +1070,7 @@
         <v>125760046</v>
       </c>
       <c r="B6" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125760093</v>
+        <v>125760092</v>
       </c>
       <c r="B7" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>773964</v>
+        <v>773927</v>
       </c>
       <c r="R7" t="n">
-        <v>7176602</v>
+        <v>7176601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125760092</v>
+        <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>773927</v>
+        <v>773964</v>
       </c>
       <c r="R8" t="n">
-        <v>7176601</v>
+        <v>7176602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760094</v>
+        <v>125760071</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>91686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774050</v>
+        <v>774022</v>
       </c>
       <c r="R9" t="n">
-        <v>7176592</v>
+        <v>7176810</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760071</v>
+        <v>125760090</v>
       </c>
       <c r="B10" t="n">
-        <v>91682</v>
+        <v>98338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774022</v>
+        <v>773892</v>
       </c>
       <c r="R10" t="n">
-        <v>7176810</v>
+        <v>7176629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760090</v>
+        <v>125760094</v>
       </c>
       <c r="B11" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>773892</v>
+        <v>774050</v>
       </c>
       <c r="R11" t="n">
-        <v>7176629</v>
+        <v>7176592</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125760106</v>
+        <v>125760119</v>
       </c>
       <c r="B12" t="n">
-        <v>98334</v>
+        <v>80110</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>773963</v>
+        <v>773979</v>
       </c>
       <c r="R12" t="n">
-        <v>7176727</v>
+        <v>7176725</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760119</v>
+        <v>125760056</v>
       </c>
       <c r="B13" t="n">
-        <v>80106</v>
+        <v>91232</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>773979</v>
+        <v>773968</v>
       </c>
       <c r="R13" t="n">
-        <v>7176725</v>
+        <v>7176780</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125760056</v>
+        <v>125760106</v>
       </c>
       <c r="B16" t="n">
-        <v>91228</v>
+        <v>98338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>773968</v>
+        <v>773963</v>
       </c>
       <c r="R16" t="n">
-        <v>7176780</v>
+        <v>7176727</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125760089</v>
+        <v>125760114</v>
       </c>
       <c r="B17" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>773952</v>
+        <v>773976</v>
       </c>
       <c r="R17" t="n">
-        <v>7176706</v>
+        <v>7176802</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125760114</v>
+        <v>125760084</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>773976</v>
+        <v>773979</v>
       </c>
       <c r="R18" t="n">
-        <v>7176802</v>
+        <v>7176725</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125760084</v>
+        <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>773979</v>
+        <v>773952</v>
       </c>
       <c r="R19" t="n">
-        <v>7176725</v>
+        <v>7176706</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125760081</v>
+        <v>125760058</v>
       </c>
       <c r="B20" t="n">
-        <v>80099</v>
+        <v>91232</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>773937</v>
+        <v>774022</v>
       </c>
       <c r="R20" t="n">
-        <v>7176636</v>
+        <v>7176810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125760058</v>
+        <v>125760081</v>
       </c>
       <c r="B21" t="n">
-        <v>91228</v>
+        <v>80103</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>774022</v>
+        <v>773937</v>
       </c>
       <c r="R21" t="n">
-        <v>7176810</v>
+        <v>7176636</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125760110</v>
+        <v>125760082</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>774041</v>
+        <v>773931</v>
       </c>
       <c r="R22" t="n">
-        <v>7176829</v>
+        <v>7176699</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125760082</v>
+        <v>125760057</v>
       </c>
       <c r="B23" t="n">
-        <v>80071</v>
+        <v>91232</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>773931</v>
+        <v>774006</v>
       </c>
       <c r="R23" t="n">
-        <v>7176699</v>
+        <v>7176806</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
         <v>125760066</v>
       </c>
       <c r="B24" t="n">
-        <v>91178</v>
+        <v>91182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125760057</v>
+        <v>125760110</v>
       </c>
       <c r="B25" t="n">
-        <v>91228</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>774006</v>
+        <v>774041</v>
       </c>
       <c r="R25" t="n">
-        <v>7176806</v>
+        <v>7176829</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3011,7 +3011,7 @@
         <v>125760111</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125760059</v>
+        <v>125760045</v>
       </c>
       <c r="B27" t="n">
-        <v>91925</v>
+        <v>79004</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>774009</v>
+        <v>773995</v>
       </c>
       <c r="R27" t="n">
-        <v>7176814</v>
+        <v>7176808</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125760045</v>
+        <v>125760059</v>
       </c>
       <c r="B28" t="n">
-        <v>79000</v>
+        <v>91929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>773995</v>
+        <v>774009</v>
       </c>
       <c r="R28" t="n">
-        <v>7176808</v>
+        <v>7176814</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125760085</v>
+        <v>125760073</v>
       </c>
       <c r="B29" t="n">
-        <v>80071</v>
+        <v>91528</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>774028</v>
+        <v>773962</v>
       </c>
       <c r="R29" t="n">
-        <v>7176813</v>
+        <v>7176754</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125760073</v>
+        <v>125760085</v>
       </c>
       <c r="B30" t="n">
-        <v>91524</v>
+        <v>80075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>773962</v>
+        <v>774028</v>
       </c>
       <c r="R30" t="n">
-        <v>7176754</v>
+        <v>7176813</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125760067</v>
+        <v>125760050</v>
       </c>
       <c r="B31" t="n">
-        <v>91178</v>
+        <v>91232</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>774003</v>
+        <v>773962</v>
       </c>
       <c r="R31" t="n">
-        <v>7176722</v>
+        <v>7176754</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125760050</v>
+        <v>125760067</v>
       </c>
       <c r="B32" t="n">
-        <v>91228</v>
+        <v>91182</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>773962</v>
+        <v>774003</v>
       </c>
       <c r="R32" t="n">
-        <v>7176754</v>
+        <v>7176722</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125760048</v>
+        <v>125760055</v>
       </c>
       <c r="B33" t="n">
-        <v>91193</v>
+        <v>91232</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>774008</v>
+        <v>773997</v>
       </c>
       <c r="R33" t="n">
-        <v>7176756</v>
+        <v>7176755</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
         <v>125760044</v>
       </c>
       <c r="B34" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,32 +3881,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125760055</v>
+        <v>125760048</v>
       </c>
       <c r="B35" t="n">
-        <v>91228</v>
+        <v>91197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>773997</v>
+        <v>774008</v>
       </c>
       <c r="R35" t="n">
-        <v>7176755</v>
+        <v>7176756</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3981,7 +3981,7 @@
         <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>91586</v>
+        <v>91590</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>125760113</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,32 +4269,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125760091</v>
+        <v>125760077</v>
       </c>
       <c r="B39" t="n">
-        <v>98334</v>
+        <v>91528</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>773895</v>
+        <v>773963</v>
       </c>
       <c r="R39" t="n">
-        <v>7176617</v>
+        <v>7176727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125760077</v>
+        <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>91524</v>
+        <v>98338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>773963</v>
+        <v>773895</v>
       </c>
       <c r="R40" t="n">
-        <v>7176727</v>
+        <v>7176617</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125760064</v>
+        <v>125760105</v>
       </c>
       <c r="B42" t="n">
-        <v>57811</v>
+        <v>98338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>773973</v>
+        <v>773966</v>
       </c>
       <c r="R42" t="n">
-        <v>7176728</v>
+        <v>7176724</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125760105</v>
+        <v>125760064</v>
       </c>
       <c r="B43" t="n">
-        <v>98334</v>
+        <v>57811</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>773966</v>
+        <v>773973</v>
       </c>
       <c r="R43" t="n">
-        <v>7176724</v>
+        <v>7176728</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4757,7 +4757,7 @@
         <v>125760065</v>
       </c>
       <c r="B44" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125760117</v>
+        <v>125760118</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>88641</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4972,41 +4972,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>774183</v>
+        <v>774109</v>
       </c>
       <c r="R46" t="n">
-        <v>7176785</v>
+        <v>7176799</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5047,7 +5040,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5066,10 +5058,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125760118</v>
+        <v>125760117</v>
       </c>
       <c r="B47" t="n">
-        <v>88637</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5077,34 +5069,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>774109</v>
+        <v>774183</v>
       </c>
       <c r="R47" t="n">
-        <v>7176799</v>
+        <v>7176785</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5145,6 +5144,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760116</v>
+        <v>125760095</v>
       </c>
       <c r="B48" t="n">
-        <v>98251</v>
+        <v>98338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774119</v>
+        <v>774109</v>
       </c>
       <c r="R48" t="n">
-        <v>7176822</v>
+        <v>7176695</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760095</v>
+        <v>125760100</v>
       </c>
       <c r="B49" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774109</v>
+        <v>774165</v>
       </c>
       <c r="R49" t="n">
-        <v>7176695</v>
+        <v>7176738</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,10 +5357,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760100</v>
+        <v>125760096</v>
       </c>
       <c r="B50" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774165</v>
+        <v>774131</v>
       </c>
       <c r="R50" t="n">
-        <v>7176738</v>
+        <v>7176720</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760096</v>
+        <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98334</v>
+        <v>98255</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774131</v>
+        <v>774119</v>
       </c>
       <c r="R51" t="n">
-        <v>7176720</v>
+        <v>7176822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5554,7 +5554,7 @@
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125760099</v>
+        <v>125760062</v>
       </c>
       <c r="B53" t="n">
-        <v>98334</v>
+        <v>57811</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>774146</v>
+        <v>774110</v>
       </c>
       <c r="R53" t="n">
-        <v>7176735</v>
+        <v>7176824</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,32 +5745,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125760062</v>
+        <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>57811</v>
+        <v>98338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>774110</v>
+        <v>774146</v>
       </c>
       <c r="R54" t="n">
-        <v>7176824</v>
+        <v>7176735</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125760052</v>
+        <v>125760115</v>
       </c>
       <c r="B55" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>774143</v>
+        <v>774095</v>
       </c>
       <c r="R55" t="n">
-        <v>7176723</v>
+        <v>7176826</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5913,6 +5913,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5939,10 +5944,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125760115</v>
+        <v>125760052</v>
       </c>
       <c r="B56" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5950,21 +5955,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5974,10 +5979,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>774095</v>
+        <v>774143</v>
       </c>
       <c r="R56" t="n">
-        <v>7176826</v>
+        <v>7176723</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6010,11 +6015,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6041,32 +6041,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125760097</v>
+        <v>125760076</v>
       </c>
       <c r="B57" t="n">
-        <v>98334</v>
+        <v>91528</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>774142</v>
+        <v>774175</v>
       </c>
       <c r="R57" t="n">
-        <v>7176720</v>
+        <v>7176775</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6138,48 +6138,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125760086</v>
+        <v>125760061</v>
       </c>
       <c r="B58" t="n">
-        <v>91429</v>
+        <v>57811</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>774175</v>
+        <v>774115</v>
       </c>
       <c r="R58" t="n">
-        <v>7176775</v>
+        <v>7176821</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6220,7 +6217,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6239,35 +6235,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760076</v>
+        <v>125760086</v>
       </c>
       <c r="B59" t="n">
-        <v>91524</v>
+        <v>91433</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
@@ -6318,6 +6317,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6336,32 +6336,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125760061</v>
+        <v>125760097</v>
       </c>
       <c r="B60" t="n">
-        <v>57811</v>
+        <v>98338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>774115</v>
+        <v>774142</v>
       </c>
       <c r="R60" t="n">
-        <v>7176821</v>
+        <v>7176720</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6436,7 +6436,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>125760108</v>
       </c>
       <c r="B62" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>125760072</v>
       </c>
       <c r="B63" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>125760053</v>
       </c>
       <c r="B65" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>125760074</v>
       </c>
       <c r="B66" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7016,32 +7016,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125760109</v>
+        <v>125760103</v>
       </c>
       <c r="B67" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>774182</v>
+        <v>774172</v>
       </c>
       <c r="R67" t="n">
-        <v>7176808</v>
+        <v>7176751</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125760103</v>
+        <v>125760109</v>
       </c>
       <c r="B68" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>774172</v>
+        <v>774182</v>
       </c>
       <c r="R68" t="n">
-        <v>7176751</v>
+        <v>7176808</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91635</v>
+        <v>91639</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125760045</v>
+        <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>79004</v>
+        <v>91929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>773995</v>
+        <v>774009</v>
       </c>
       <c r="R27" t="n">
-        <v>7176808</v>
+        <v>7176814</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125760059</v>
+        <v>125760045</v>
       </c>
       <c r="B28" t="n">
-        <v>91929</v>
+        <v>79004</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>774009</v>
+        <v>773995</v>
       </c>
       <c r="R28" t="n">
-        <v>7176814</v>
+        <v>7176808</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125760055</v>
+        <v>125760044</v>
       </c>
       <c r="B33" t="n">
-        <v>91232</v>
+        <v>79004</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3698,21 +3698,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>773997</v>
+        <v>774005</v>
       </c>
       <c r="R33" t="n">
-        <v>7176755</v>
+        <v>7176711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,32 +3784,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125760044</v>
+        <v>125760048</v>
       </c>
       <c r="B34" t="n">
-        <v>79004</v>
+        <v>91197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>774005</v>
+        <v>774008</v>
       </c>
       <c r="R34" t="n">
-        <v>7176711</v>
+        <v>7176756</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3881,32 +3881,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125760048</v>
+        <v>125760055</v>
       </c>
       <c r="B35" t="n">
-        <v>91197</v>
+        <v>91232</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>774008</v>
+        <v>773997</v>
       </c>
       <c r="R35" t="n">
-        <v>7176756</v>
+        <v>7176755</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -6138,45 +6138,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125760061</v>
+        <v>125760086</v>
       </c>
       <c r="B58" t="n">
-        <v>57811</v>
+        <v>91433</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>48</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>774115</v>
+        <v>774175</v>
       </c>
       <c r="R58" t="n">
-        <v>7176821</v>
+        <v>7176775</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6217,6 +6220,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6235,48 +6239,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760086</v>
+        <v>125760061</v>
       </c>
       <c r="B59" t="n">
-        <v>91433</v>
+        <v>57811</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>774175</v>
+        <v>774115</v>
       </c>
       <c r="R59" t="n">
-        <v>7176775</v>
+        <v>7176821</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6317,7 +6318,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -772,48 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125760088</v>
+        <v>125760112</v>
       </c>
       <c r="B3" t="n">
-        <v>91819</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774000</v>
+        <v>774025</v>
       </c>
       <c r="R3" t="n">
-        <v>7176753</v>
+        <v>7176810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,45 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125760051</v>
+        <v>125760088</v>
       </c>
       <c r="B4" t="n">
-        <v>91232</v>
+        <v>91819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>773924</v>
+        <v>774000</v>
       </c>
       <c r="R4" t="n">
-        <v>7176602</v>
+        <v>7176753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125760112</v>
+        <v>125760051</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774025</v>
+        <v>773924</v>
       </c>
       <c r="R5" t="n">
-        <v>7176810</v>
+        <v>7176602</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>125760092</v>
       </c>
       <c r="B7" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760071</v>
+        <v>125760090</v>
       </c>
       <c r="B9" t="n">
-        <v>91686</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774022</v>
+        <v>773892</v>
       </c>
       <c r="R9" t="n">
-        <v>7176810</v>
+        <v>7176629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760090</v>
+        <v>125760094</v>
       </c>
       <c r="B10" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>773892</v>
+        <v>774050</v>
       </c>
       <c r="R10" t="n">
-        <v>7176629</v>
+        <v>7176592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760094</v>
+        <v>125760071</v>
       </c>
       <c r="B11" t="n">
-        <v>98338</v>
+        <v>91686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774050</v>
+        <v>774022</v>
       </c>
       <c r="R11" t="n">
-        <v>7176592</v>
+        <v>7176810</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760056</v>
+        <v>125760070</v>
       </c>
       <c r="B13" t="n">
-        <v>91232</v>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>773968</v>
+        <v>774000</v>
       </c>
       <c r="R13" t="n">
-        <v>7176780</v>
+        <v>7176761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125760070</v>
+        <v>125760056</v>
       </c>
       <c r="B15" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774000</v>
+        <v>773968</v>
       </c>
       <c r="R15" t="n">
-        <v>7176761</v>
+        <v>7176780</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>125760106</v>
       </c>
       <c r="B16" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125760114</v>
+        <v>125760089</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>773976</v>
+        <v>773952</v>
       </c>
       <c r="R17" t="n">
-        <v>7176802</v>
+        <v>7176706</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125760084</v>
+        <v>125760114</v>
       </c>
       <c r="B18" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>773979</v>
+        <v>773976</v>
       </c>
       <c r="R18" t="n">
-        <v>7176725</v>
+        <v>7176802</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125760089</v>
+        <v>125760084</v>
       </c>
       <c r="B19" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>773952</v>
+        <v>773979</v>
       </c>
       <c r="R19" t="n">
-        <v>7176706</v>
+        <v>7176725</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125760057</v>
+        <v>125760066</v>
       </c>
       <c r="B23" t="n">
-        <v>91232</v>
+        <v>91182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
         <v>774006</v>
       </c>
       <c r="R23" t="n">
-        <v>7176806</v>
+        <v>7176718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125760066</v>
+        <v>125760110</v>
       </c>
       <c r="B24" t="n">
-        <v>91182</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>774006</v>
+        <v>774041</v>
       </c>
       <c r="R24" t="n">
-        <v>7176718</v>
+        <v>7176829</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125760110</v>
+        <v>125760057</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>774041</v>
+        <v>774006</v>
       </c>
       <c r="R25" t="n">
-        <v>7176829</v>
+        <v>7176806</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125760059</v>
+        <v>125760045</v>
       </c>
       <c r="B27" t="n">
-        <v>91929</v>
+        <v>79004</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>774009</v>
+        <v>773995</v>
       </c>
       <c r="R27" t="n">
-        <v>7176814</v>
+        <v>7176808</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125760045</v>
+        <v>125760059</v>
       </c>
       <c r="B28" t="n">
-        <v>79004</v>
+        <v>91929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>773995</v>
+        <v>774009</v>
       </c>
       <c r="R28" t="n">
-        <v>7176808</v>
+        <v>7176814</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125760073</v>
+        <v>125760085</v>
       </c>
       <c r="B29" t="n">
-        <v>91528</v>
+        <v>80075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>773962</v>
+        <v>774028</v>
       </c>
       <c r="R29" t="n">
-        <v>7176754</v>
+        <v>7176813</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125760085</v>
+        <v>125760073</v>
       </c>
       <c r="B30" t="n">
-        <v>80075</v>
+        <v>91528</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>774028</v>
+        <v>773962</v>
       </c>
       <c r="R30" t="n">
-        <v>7176813</v>
+        <v>7176754</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125760050</v>
+        <v>125760067</v>
       </c>
       <c r="B31" t="n">
-        <v>91232</v>
+        <v>91182</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>773962</v>
+        <v>774003</v>
       </c>
       <c r="R31" t="n">
-        <v>7176754</v>
+        <v>7176722</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125760067</v>
+        <v>125760050</v>
       </c>
       <c r="B32" t="n">
-        <v>91182</v>
+        <v>91232</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>774003</v>
+        <v>773962</v>
       </c>
       <c r="R32" t="n">
-        <v>7176722</v>
+        <v>7176754</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125760044</v>
+        <v>125760048</v>
       </c>
       <c r="B33" t="n">
-        <v>79004</v>
+        <v>91197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>774005</v>
+        <v>774008</v>
       </c>
       <c r="R33" t="n">
-        <v>7176711</v>
+        <v>7176756</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,32 +3784,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125760048</v>
+        <v>125760055</v>
       </c>
       <c r="B34" t="n">
-        <v>91197</v>
+        <v>91232</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>774008</v>
+        <v>773997</v>
       </c>
       <c r="R34" t="n">
-        <v>7176756</v>
+        <v>7176755</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125760055</v>
+        <v>125760044</v>
       </c>
       <c r="B35" t="n">
-        <v>91232</v>
+        <v>79004</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>773997</v>
+        <v>774005</v>
       </c>
       <c r="R35" t="n">
-        <v>7176755</v>
+        <v>7176711</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4369,7 +4369,7 @@
         <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125760105</v>
+        <v>125760064</v>
       </c>
       <c r="B42" t="n">
-        <v>98338</v>
+        <v>57811</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>773966</v>
+        <v>773973</v>
       </c>
       <c r="R42" t="n">
-        <v>7176724</v>
+        <v>7176728</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125760064</v>
+        <v>125760105</v>
       </c>
       <c r="B43" t="n">
-        <v>57811</v>
+        <v>98339</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>773973</v>
+        <v>773966</v>
       </c>
       <c r="R43" t="n">
-        <v>7176728</v>
+        <v>7176724</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760095</v>
+        <v>125760116</v>
       </c>
       <c r="B48" t="n">
-        <v>98338</v>
+        <v>98256</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774109</v>
+        <v>774119</v>
       </c>
       <c r="R48" t="n">
-        <v>7176695</v>
+        <v>7176822</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760100</v>
+        <v>125760095</v>
       </c>
       <c r="B49" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774165</v>
+        <v>774109</v>
       </c>
       <c r="R49" t="n">
-        <v>7176738</v>
+        <v>7176695</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,10 +5357,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760096</v>
+        <v>125760100</v>
       </c>
       <c r="B50" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774131</v>
+        <v>774165</v>
       </c>
       <c r="R50" t="n">
-        <v>7176720</v>
+        <v>7176738</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760116</v>
+        <v>125760096</v>
       </c>
       <c r="B51" t="n">
-        <v>98255</v>
+        <v>98339</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774119</v>
+        <v>774131</v>
       </c>
       <c r="R51" t="n">
-        <v>7176822</v>
+        <v>7176720</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
         <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6041,35 +6041,38 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125760076</v>
+        <v>125760086</v>
       </c>
       <c r="B57" t="n">
-        <v>91528</v>
+        <v>91433</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
@@ -6120,6 +6123,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6138,38 +6142,35 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125760086</v>
+        <v>125760076</v>
       </c>
       <c r="B58" t="n">
-        <v>91433</v>
+        <v>91528</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
@@ -6220,7 +6221,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>125760097</v>
       </c>
       <c r="B60" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125760072</v>
+        <v>125760063</v>
       </c>
       <c r="B63" t="n">
-        <v>91528</v>
+        <v>57811</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>774185</v>
+        <v>774078</v>
       </c>
       <c r="R63" t="n">
-        <v>7176787</v>
+        <v>7176829</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6706,7 +6706,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6725,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125760063</v>
+        <v>125760072</v>
       </c>
       <c r="B64" t="n">
-        <v>57811</v>
+        <v>91528</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6736,21 +6735,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6760,10 +6759,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>774078</v>
+        <v>774185</v>
       </c>
       <c r="R64" t="n">
-        <v>7176829</v>
+        <v>7176787</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,6 +6803,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7016,32 +7016,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125760103</v>
+        <v>125760109</v>
       </c>
       <c r="B67" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>774172</v>
+        <v>774182</v>
       </c>
       <c r="R67" t="n">
-        <v>7176751</v>
+        <v>7176808</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125760109</v>
+        <v>125760103</v>
       </c>
       <c r="B68" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>774182</v>
+        <v>774172</v>
       </c>
       <c r="R68" t="n">
-        <v>7176808</v>
+        <v>7176751</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125760119</v>
+        <v>125760070</v>
       </c>
       <c r="B12" t="n">
-        <v>80110</v>
+        <v>57648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>773979</v>
+        <v>774000</v>
       </c>
       <c r="R12" t="n">
-        <v>7176725</v>
+        <v>7176761</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760070</v>
+        <v>125760069</v>
       </c>
       <c r="B13" t="n">
         <v>57648</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>774000</v>
+        <v>774048</v>
       </c>
       <c r="R13" t="n">
-        <v>7176761</v>
+        <v>7176608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125760069</v>
+        <v>125760119</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>80110</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>774048</v>
+        <v>773979</v>
       </c>
       <c r="R14" t="n">
-        <v>7176608</v>
+        <v>7176725</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125760058</v>
+        <v>125760081</v>
       </c>
       <c r="B20" t="n">
-        <v>91232</v>
+        <v>80103</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>774022</v>
+        <v>773937</v>
       </c>
       <c r="R20" t="n">
-        <v>7176810</v>
+        <v>7176636</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125760081</v>
+        <v>125760058</v>
       </c>
       <c r="B21" t="n">
-        <v>80103</v>
+        <v>91232</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>773937</v>
+        <v>774022</v>
       </c>
       <c r="R21" t="n">
-        <v>7176636</v>
+        <v>7176810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125760048</v>
+        <v>125760044</v>
       </c>
       <c r="B33" t="n">
-        <v>91197</v>
+        <v>79004</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>774008</v>
+        <v>774005</v>
       </c>
       <c r="R33" t="n">
-        <v>7176756</v>
+        <v>7176711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,32 +3784,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125760055</v>
+        <v>125760048</v>
       </c>
       <c r="B34" t="n">
-        <v>91232</v>
+        <v>91197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>773997</v>
+        <v>774008</v>
       </c>
       <c r="R34" t="n">
-        <v>7176755</v>
+        <v>7176756</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125760044</v>
+        <v>125760055</v>
       </c>
       <c r="B35" t="n">
-        <v>79004</v>
+        <v>91232</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>774005</v>
+        <v>773997</v>
       </c>
       <c r="R35" t="n">
-        <v>7176711</v>
+        <v>7176755</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125760049</v>
+        <v>125760113</v>
       </c>
       <c r="B36" t="n">
-        <v>91590</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>773997</v>
+        <v>774009</v>
       </c>
       <c r="R36" t="n">
-        <v>7176755</v>
+        <v>7176817</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125760113</v>
+        <v>125760049</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>91590</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>774009</v>
+        <v>773997</v>
       </c>
       <c r="R37" t="n">
-        <v>7176817</v>
+        <v>7176755</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760116</v>
+        <v>125760095</v>
       </c>
       <c r="B48" t="n">
-        <v>98256</v>
+        <v>98339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774119</v>
+        <v>774109</v>
       </c>
       <c r="R48" t="n">
-        <v>7176822</v>
+        <v>7176695</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760095</v>
+        <v>125760100</v>
       </c>
       <c r="B49" t="n">
         <v>98339</v>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774109</v>
+        <v>774165</v>
       </c>
       <c r="R49" t="n">
-        <v>7176695</v>
+        <v>7176738</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,7 +5357,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760100</v>
+        <v>125760096</v>
       </c>
       <c r="B50" t="n">
         <v>98339</v>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774165</v>
+        <v>774131</v>
       </c>
       <c r="R50" t="n">
-        <v>7176738</v>
+        <v>7176720</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760096</v>
+        <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98339</v>
+        <v>98256</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774131</v>
+        <v>774119</v>
       </c>
       <c r="R51" t="n">
-        <v>7176720</v>
+        <v>7176822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125760063</v>
+        <v>125760072</v>
       </c>
       <c r="B63" t="n">
-        <v>57811</v>
+        <v>91528</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>774078</v>
+        <v>774185</v>
       </c>
       <c r="R63" t="n">
-        <v>7176829</v>
+        <v>7176787</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6706,6 +6706,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6724,10 +6725,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125760072</v>
+        <v>125760063</v>
       </c>
       <c r="B64" t="n">
-        <v>91528</v>
+        <v>57811</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6735,21 +6736,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6759,10 +6760,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>774185</v>
+        <v>774078</v>
       </c>
       <c r="R64" t="n">
-        <v>7176787</v>
+        <v>7176829</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6803,7 +6804,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125760070</v>
+        <v>125760119</v>
       </c>
       <c r="B12" t="n">
-        <v>57648</v>
+        <v>80110</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>774000</v>
+        <v>773979</v>
       </c>
       <c r="R12" t="n">
-        <v>7176761</v>
+        <v>7176725</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760069</v>
+        <v>125760070</v>
       </c>
       <c r="B13" t="n">
         <v>57648</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>774048</v>
+        <v>774000</v>
       </c>
       <c r="R13" t="n">
-        <v>7176608</v>
+        <v>7176761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125760119</v>
+        <v>125760069</v>
       </c>
       <c r="B14" t="n">
-        <v>80110</v>
+        <v>57648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>773979</v>
+        <v>774048</v>
       </c>
       <c r="R14" t="n">
-        <v>7176725</v>
+        <v>7176608</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125760089</v>
+        <v>125760114</v>
       </c>
       <c r="B17" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>773952</v>
+        <v>773976</v>
       </c>
       <c r="R17" t="n">
-        <v>7176706</v>
+        <v>7176802</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125760114</v>
+        <v>125760084</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>773976</v>
+        <v>773979</v>
       </c>
       <c r="R18" t="n">
-        <v>7176802</v>
+        <v>7176725</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125760084</v>
+        <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>773979</v>
+        <v>773952</v>
       </c>
       <c r="R19" t="n">
-        <v>7176725</v>
+        <v>7176706</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125760113</v>
+        <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>91590</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>774009</v>
+        <v>773997</v>
       </c>
       <c r="R36" t="n">
-        <v>7176817</v>
+        <v>7176755</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125760049</v>
+        <v>125760113</v>
       </c>
       <c r="B37" t="n">
-        <v>91590</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>773997</v>
+        <v>774009</v>
       </c>
       <c r="R37" t="n">
-        <v>7176755</v>
+        <v>7176817</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125760083</v>
+        <v>125760112</v>
       </c>
       <c r="B2" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774042</v>
+        <v>774025</v>
       </c>
       <c r="R2" t="n">
-        <v>7176609</v>
+        <v>7176810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125760112</v>
+        <v>125760088</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>91821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774025</v>
+        <v>774000</v>
       </c>
       <c r="R3" t="n">
-        <v>7176810</v>
+        <v>7176753</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,48 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125760088</v>
+        <v>125760051</v>
       </c>
       <c r="B4" t="n">
-        <v>91819</v>
+        <v>91234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774000</v>
+        <v>773924</v>
       </c>
       <c r="R4" t="n">
-        <v>7176753</v>
+        <v>7176602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125760051</v>
+        <v>125760083</v>
       </c>
       <c r="B5" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>773924</v>
+        <v>774042</v>
       </c>
       <c r="R5" t="n">
-        <v>7176602</v>
+        <v>7176609</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,7 +1070,7 @@
         <v>125760046</v>
       </c>
       <c r="B6" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125760092</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760090</v>
+        <v>125760071</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>91688</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>773892</v>
+        <v>774022</v>
       </c>
       <c r="R9" t="n">
-        <v>7176629</v>
+        <v>7176810</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760094</v>
+        <v>125760090</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774050</v>
+        <v>773892</v>
       </c>
       <c r="R10" t="n">
-        <v>7176592</v>
+        <v>7176629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760071</v>
+        <v>125760094</v>
       </c>
       <c r="B11" t="n">
-        <v>91686</v>
+        <v>98341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774022</v>
+        <v>774050</v>
       </c>
       <c r="R11" t="n">
-        <v>7176810</v>
+        <v>7176592</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125760119</v>
+        <v>125760056</v>
       </c>
       <c r="B12" t="n">
-        <v>80110</v>
+        <v>91234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>773979</v>
+        <v>773968</v>
       </c>
       <c r="R12" t="n">
-        <v>7176725</v>
+        <v>7176780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,7 +1750,7 @@
         <v>125760070</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>125760069</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125760056</v>
+        <v>125760119</v>
       </c>
       <c r="B15" t="n">
-        <v>91232</v>
+        <v>80111</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>773968</v>
+        <v>773979</v>
       </c>
       <c r="R15" t="n">
-        <v>7176780</v>
+        <v>7176725</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>125760106</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>125760114</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>125760084</v>
       </c>
       <c r="B18" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125760081</v>
+        <v>125760058</v>
       </c>
       <c r="B20" t="n">
-        <v>80103</v>
+        <v>91234</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>773937</v>
+        <v>774022</v>
       </c>
       <c r="R20" t="n">
-        <v>7176636</v>
+        <v>7176810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125760058</v>
+        <v>125760081</v>
       </c>
       <c r="B21" t="n">
-        <v>91232</v>
+        <v>80104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>774022</v>
+        <v>773937</v>
       </c>
       <c r="R21" t="n">
-        <v>7176810</v>
+        <v>7176636</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125760082</v>
+        <v>125760066</v>
       </c>
       <c r="B22" t="n">
-        <v>80075</v>
+        <v>91184</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>773931</v>
+        <v>774006</v>
       </c>
       <c r="R22" t="n">
-        <v>7176699</v>
+        <v>7176718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125760066</v>
+        <v>125760110</v>
       </c>
       <c r="B23" t="n">
-        <v>91182</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>774006</v>
+        <v>774041</v>
       </c>
       <c r="R23" t="n">
-        <v>7176718</v>
+        <v>7176829</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125760110</v>
+        <v>125760057</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>91234</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>774041</v>
+        <v>774006</v>
       </c>
       <c r="R24" t="n">
-        <v>7176829</v>
+        <v>7176806</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125760057</v>
+        <v>125760082</v>
       </c>
       <c r="B25" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>774006</v>
+        <v>773931</v>
       </c>
       <c r="R25" t="n">
-        <v>7176806</v>
+        <v>7176699</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3011,7 +3011,7 @@
         <v>125760111</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125760045</v>
+        <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>79004</v>
+        <v>91931</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>773995</v>
+        <v>774009</v>
       </c>
       <c r="R27" t="n">
-        <v>7176808</v>
+        <v>7176814</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125760059</v>
+        <v>125760045</v>
       </c>
       <c r="B28" t="n">
-        <v>91929</v>
+        <v>79005</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>774009</v>
+        <v>773995</v>
       </c>
       <c r="R28" t="n">
-        <v>7176814</v>
+        <v>7176808</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125760085</v>
+        <v>125760073</v>
       </c>
       <c r="B29" t="n">
-        <v>80075</v>
+        <v>91530</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>774028</v>
+        <v>773962</v>
       </c>
       <c r="R29" t="n">
-        <v>7176813</v>
+        <v>7176754</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125760073</v>
+        <v>125760085</v>
       </c>
       <c r="B30" t="n">
-        <v>91528</v>
+        <v>80076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>773962</v>
+        <v>774028</v>
       </c>
       <c r="R30" t="n">
-        <v>7176754</v>
+        <v>7176813</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125760067</v>
+        <v>125760050</v>
       </c>
       <c r="B31" t="n">
-        <v>91182</v>
+        <v>91234</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>774003</v>
+        <v>773962</v>
       </c>
       <c r="R31" t="n">
-        <v>7176722</v>
+        <v>7176754</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125760050</v>
+        <v>125760067</v>
       </c>
       <c r="B32" t="n">
-        <v>91232</v>
+        <v>91184</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>773962</v>
+        <v>774003</v>
       </c>
       <c r="R32" t="n">
-        <v>7176754</v>
+        <v>7176722</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125760044</v>
+        <v>125760048</v>
       </c>
       <c r="B33" t="n">
-        <v>79004</v>
+        <v>91199</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>774005</v>
+        <v>774008</v>
       </c>
       <c r="R33" t="n">
-        <v>7176711</v>
+        <v>7176756</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,32 +3784,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125760048</v>
+        <v>125760055</v>
       </c>
       <c r="B34" t="n">
-        <v>91197</v>
+        <v>91234</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>774008</v>
+        <v>773997</v>
       </c>
       <c r="R34" t="n">
-        <v>7176756</v>
+        <v>7176755</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125760055</v>
+        <v>125760044</v>
       </c>
       <c r="B35" t="n">
-        <v>91232</v>
+        <v>79005</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>773997</v>
+        <v>774005</v>
       </c>
       <c r="R35" t="n">
-        <v>7176755</v>
+        <v>7176711</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3981,7 +3981,7 @@
         <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>91590</v>
+        <v>91592</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>125760113</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>125760077</v>
       </c>
       <c r="B39" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>125760064</v>
       </c>
       <c r="B42" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>125760105</v>
       </c>
       <c r="B43" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>125760065</v>
       </c>
       <c r="B44" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>125760068</v>
       </c>
       <c r="B45" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125760118</v>
+        <v>125760117</v>
       </c>
       <c r="B46" t="n">
-        <v>88641</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4972,34 +4972,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>774109</v>
+        <v>774183</v>
       </c>
       <c r="R46" t="n">
-        <v>7176799</v>
+        <v>7176785</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5040,6 +5047,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5058,10 +5066,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125760117</v>
+        <v>125760118</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>88643</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5069,41 +5077,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>774183</v>
+        <v>774109</v>
       </c>
       <c r="R47" t="n">
-        <v>7176785</v>
+        <v>7176799</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5144,7 +5145,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>125760095</v>
       </c>
       <c r="B48" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>125760100</v>
       </c>
       <c r="B49" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5357,32 +5357,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760096</v>
+        <v>125760116</v>
       </c>
       <c r="B50" t="n">
-        <v>98339</v>
+        <v>98258</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774131</v>
+        <v>774119</v>
       </c>
       <c r="R50" t="n">
-        <v>7176720</v>
+        <v>7176822</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760116</v>
+        <v>125760096</v>
       </c>
       <c r="B51" t="n">
-        <v>98256</v>
+        <v>98341</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774119</v>
+        <v>774131</v>
       </c>
       <c r="R51" t="n">
-        <v>7176822</v>
+        <v>7176720</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5554,7 +5554,7 @@
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>125760062</v>
       </c>
       <c r="B53" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>125760115</v>
       </c>
       <c r="B55" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>125760052</v>
       </c>
       <c r="B56" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6041,48 +6041,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125760086</v>
+        <v>125760061</v>
       </c>
       <c r="B57" t="n">
-        <v>91433</v>
+        <v>57812</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>774175</v>
+        <v>774115</v>
       </c>
       <c r="R57" t="n">
-        <v>7176775</v>
+        <v>7176821</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6123,7 +6120,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6142,35 +6138,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125760076</v>
+        <v>125760086</v>
       </c>
       <c r="B58" t="n">
-        <v>91528</v>
+        <v>91435</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
@@ -6221,6 +6220,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760061</v>
+        <v>125760076</v>
       </c>
       <c r="B59" t="n">
-        <v>57811</v>
+        <v>91530</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>774115</v>
+        <v>774175</v>
       </c>
       <c r="R59" t="n">
-        <v>7176821</v>
+        <v>7176775</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6339,7 +6339,7 @@
         <v>125760097</v>
       </c>
       <c r="B60" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>125760108</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>125760072</v>
       </c>
       <c r="B63" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>125760063</v>
       </c>
       <c r="B64" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>125760053</v>
       </c>
       <c r="B65" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>125760074</v>
       </c>
       <c r="B66" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>125760109</v>
       </c>
       <c r="B67" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>125760103</v>
       </c>
       <c r="B68" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>125760080</v>
       </c>
       <c r="B74" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -4961,10 +4961,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125760117</v>
+        <v>125760118</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>88643</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4972,41 +4972,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>774183</v>
+        <v>774109</v>
       </c>
       <c r="R46" t="n">
-        <v>7176785</v>
+        <v>7176799</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5047,7 +5040,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5066,10 +5058,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125760118</v>
+        <v>125760117</v>
       </c>
       <c r="B47" t="n">
-        <v>88643</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5077,34 +5069,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>774109</v>
+        <v>774183</v>
       </c>
       <c r="R47" t="n">
-        <v>7176799</v>
+        <v>7176785</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5145,6 +5144,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125760115</v>
+        <v>125760052</v>
       </c>
       <c r="B55" t="n">
-        <v>57652</v>
+        <v>91234</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>774095</v>
+        <v>774143</v>
       </c>
       <c r="R55" t="n">
-        <v>7176826</v>
+        <v>7176723</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5913,11 +5913,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5944,10 +5939,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125760052</v>
+        <v>125760115</v>
       </c>
       <c r="B56" t="n">
-        <v>91234</v>
+        <v>57652</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5955,21 +5950,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5979,10 +5974,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>774143</v>
+        <v>774095</v>
       </c>
       <c r="R56" t="n">
-        <v>7176723</v>
+        <v>7176826</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6015,6 +6010,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6138,10 +6138,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125760086</v>
+        <v>125760097</v>
       </c>
       <c r="B58" t="n">
-        <v>91435</v>
+        <v>98341</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6149,37 +6149,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>774175</v>
+        <v>774142</v>
       </c>
       <c r="R58" t="n">
-        <v>7176775</v>
+        <v>7176720</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6220,7 +6217,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6239,35 +6235,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760076</v>
+        <v>125760086</v>
       </c>
       <c r="B59" t="n">
-        <v>91530</v>
+        <v>91435</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
@@ -6318,6 +6317,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6336,32 +6336,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125760097</v>
+        <v>125760076</v>
       </c>
       <c r="B60" t="n">
-        <v>98341</v>
+        <v>91530</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>774142</v>
+        <v>774175</v>
       </c>
       <c r="R60" t="n">
-        <v>7176720</v>
+        <v>7176775</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125760088</v>
       </c>
       <c r="B3" t="n">
-        <v>91821</v>
+        <v>91823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>125760051</v>
       </c>
       <c r="B4" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125760046</v>
+        <v>125760092</v>
       </c>
       <c r="B6" t="n">
-        <v>79005</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>773999</v>
+        <v>773927</v>
       </c>
       <c r="R6" t="n">
-        <v>7176749</v>
+        <v>7176601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,7 +1146,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1165,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125760092</v>
+        <v>125760093</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>773927</v>
+        <v>773964</v>
       </c>
       <c r="R7" t="n">
-        <v>7176601</v>
+        <v>7176602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1261,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125760093</v>
+        <v>125760046</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>79005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>773964</v>
+        <v>773999</v>
       </c>
       <c r="R8" t="n">
-        <v>7176602</v>
+        <v>7176749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,6 +1340,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760071</v>
+        <v>125760090</v>
       </c>
       <c r="B9" t="n">
-        <v>91688</v>
+        <v>98343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774022</v>
+        <v>773892</v>
       </c>
       <c r="R9" t="n">
-        <v>7176810</v>
+        <v>7176629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760090</v>
+        <v>125760094</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>773892</v>
+        <v>774050</v>
       </c>
       <c r="R10" t="n">
-        <v>7176629</v>
+        <v>7176592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760094</v>
+        <v>125760071</v>
       </c>
       <c r="B11" t="n">
-        <v>98341</v>
+        <v>91690</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774050</v>
+        <v>774022</v>
       </c>
       <c r="R11" t="n">
-        <v>7176592</v>
+        <v>7176810</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,7 +1653,7 @@
         <v>125760056</v>
       </c>
       <c r="B12" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760070</v>
+        <v>125760069</v>
       </c>
       <c r="B13" t="n">
         <v>57649</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>774000</v>
+        <v>774048</v>
       </c>
       <c r="R13" t="n">
-        <v>7176761</v>
+        <v>7176608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125760069</v>
+        <v>125760070</v>
       </c>
       <c r="B14" t="n">
         <v>57649</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>774048</v>
+        <v>774000</v>
       </c>
       <c r="R14" t="n">
-        <v>7176608</v>
+        <v>7176761</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125760119</v>
+        <v>125760106</v>
       </c>
       <c r="B15" t="n">
-        <v>80111</v>
+        <v>98343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>773979</v>
+        <v>773963</v>
       </c>
       <c r="R15" t="n">
-        <v>7176725</v>
+        <v>7176727</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125760106</v>
+        <v>125760119</v>
       </c>
       <c r="B16" t="n">
-        <v>98341</v>
+        <v>80111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>773963</v>
+        <v>773979</v>
       </c>
       <c r="R16" t="n">
-        <v>7176727</v>
+        <v>7176725</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125760114</v>
+        <v>125760089</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>773976</v>
+        <v>773952</v>
       </c>
       <c r="R17" t="n">
-        <v>7176802</v>
+        <v>7176706</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125760084</v>
+        <v>125760114</v>
       </c>
       <c r="B18" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>773979</v>
+        <v>773976</v>
       </c>
       <c r="R18" t="n">
-        <v>7176725</v>
+        <v>7176802</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125760089</v>
+        <v>125760084</v>
       </c>
       <c r="B19" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>773952</v>
+        <v>773979</v>
       </c>
       <c r="R19" t="n">
-        <v>7176706</v>
+        <v>7176725</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125760058</v>
+        <v>125760081</v>
       </c>
       <c r="B20" t="n">
-        <v>91234</v>
+        <v>80104</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>774022</v>
+        <v>773937</v>
       </c>
       <c r="R20" t="n">
-        <v>7176810</v>
+        <v>7176636</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125760081</v>
+        <v>125760058</v>
       </c>
       <c r="B21" t="n">
-        <v>80104</v>
+        <v>91236</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>773937</v>
+        <v>774022</v>
       </c>
       <c r="R21" t="n">
-        <v>7176636</v>
+        <v>7176810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
         <v>125760066</v>
       </c>
       <c r="B22" t="n">
-        <v>91184</v>
+        <v>91186</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125760110</v>
+        <v>125760057</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>91236</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>774041</v>
+        <v>774006</v>
       </c>
       <c r="R23" t="n">
-        <v>7176829</v>
+        <v>7176806</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125760057</v>
+        <v>125760110</v>
       </c>
       <c r="B24" t="n">
-        <v>91234</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>774006</v>
+        <v>774041</v>
       </c>
       <c r="R24" t="n">
-        <v>7176806</v>
+        <v>7176829</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,7 +3108,7 @@
         <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>91931</v>
+        <v>91933</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>125760073</v>
       </c>
       <c r="B29" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125760050</v>
+        <v>125760067</v>
       </c>
       <c r="B31" t="n">
-        <v>91234</v>
+        <v>91186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>773962</v>
+        <v>774003</v>
       </c>
       <c r="R31" t="n">
-        <v>7176754</v>
+        <v>7176722</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125760067</v>
+        <v>125760050</v>
       </c>
       <c r="B32" t="n">
-        <v>91184</v>
+        <v>91236</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>774003</v>
+        <v>773962</v>
       </c>
       <c r="R32" t="n">
-        <v>7176722</v>
+        <v>7176754</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3690,7 +3690,7 @@
         <v>125760048</v>
       </c>
       <c r="B33" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125760055</v>
+        <v>125760044</v>
       </c>
       <c r="B34" t="n">
-        <v>91234</v>
+        <v>79005</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>773997</v>
+        <v>774005</v>
       </c>
       <c r="R34" t="n">
-        <v>7176755</v>
+        <v>7176711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125760044</v>
+        <v>125760055</v>
       </c>
       <c r="B35" t="n">
-        <v>79005</v>
+        <v>91236</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>774005</v>
+        <v>773997</v>
       </c>
       <c r="R35" t="n">
-        <v>7176711</v>
+        <v>7176755</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3981,7 +3981,7 @@
         <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>91592</v>
+        <v>91594</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>125760077</v>
       </c>
       <c r="B39" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>125760105</v>
       </c>
       <c r="B43" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>125760118</v>
       </c>
       <c r="B46" t="n">
-        <v>88643</v>
+        <v>88645</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760095</v>
+        <v>125760116</v>
       </c>
       <c r="B48" t="n">
-        <v>98341</v>
+        <v>98260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774109</v>
+        <v>774119</v>
       </c>
       <c r="R48" t="n">
-        <v>7176695</v>
+        <v>7176822</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760100</v>
+        <v>125760095</v>
       </c>
       <c r="B49" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774165</v>
+        <v>774109</v>
       </c>
       <c r="R49" t="n">
-        <v>7176738</v>
+        <v>7176695</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,32 +5357,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760116</v>
+        <v>125760100</v>
       </c>
       <c r="B50" t="n">
-        <v>98258</v>
+        <v>98343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774119</v>
+        <v>774165</v>
       </c>
       <c r="R50" t="n">
-        <v>7176822</v>
+        <v>7176738</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5457,7 +5457,7 @@
         <v>125760096</v>
       </c>
       <c r="B51" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125760062</v>
+        <v>125760099</v>
       </c>
       <c r="B53" t="n">
-        <v>57812</v>
+        <v>98343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>774110</v>
+        <v>774146</v>
       </c>
       <c r="R53" t="n">
-        <v>7176824</v>
+        <v>7176735</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,32 +5745,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125760099</v>
+        <v>125760062</v>
       </c>
       <c r="B54" t="n">
-        <v>98341</v>
+        <v>57812</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>774146</v>
+        <v>774110</v>
       </c>
       <c r="R54" t="n">
-        <v>7176735</v>
+        <v>7176824</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5845,7 +5845,7 @@
         <v>125760052</v>
       </c>
       <c r="B55" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6041,45 +6041,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125760061</v>
+        <v>125760086</v>
       </c>
       <c r="B57" t="n">
-        <v>57812</v>
+        <v>91437</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>48</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>774115</v>
+        <v>774175</v>
       </c>
       <c r="R57" t="n">
-        <v>7176821</v>
+        <v>7176775</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6120,6 +6123,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6138,32 +6142,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125760097</v>
+        <v>125760076</v>
       </c>
       <c r="B58" t="n">
-        <v>98341</v>
+        <v>91532</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6173,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>774142</v>
+        <v>774175</v>
       </c>
       <c r="R58" t="n">
-        <v>7176720</v>
+        <v>7176775</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6235,48 +6239,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760086</v>
+        <v>125760061</v>
       </c>
       <c r="B59" t="n">
-        <v>91435</v>
+        <v>57812</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>774175</v>
+        <v>774115</v>
       </c>
       <c r="R59" t="n">
-        <v>7176775</v>
+        <v>7176821</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6317,7 +6318,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6336,32 +6336,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125760076</v>
+        <v>125760097</v>
       </c>
       <c r="B60" t="n">
-        <v>91530</v>
+        <v>98343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>774175</v>
+        <v>774142</v>
       </c>
       <c r="R60" t="n">
-        <v>7176775</v>
+        <v>7176720</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6436,7 +6436,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125760108</v>
+        <v>125760063</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>774201</v>
+        <v>774078</v>
       </c>
       <c r="R62" t="n">
-        <v>7176809</v>
+        <v>7176829</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
         <v>125760072</v>
       </c>
       <c r="B63" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125760063</v>
+        <v>125760108</v>
       </c>
       <c r="B64" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>774078</v>
+        <v>774201</v>
       </c>
       <c r="R64" t="n">
-        <v>7176829</v>
+        <v>7176809</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125760053</v>
+        <v>125760074</v>
       </c>
       <c r="B65" t="n">
-        <v>91234</v>
+        <v>91532</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>774161</v>
+        <v>774149</v>
       </c>
       <c r="R65" t="n">
-        <v>7176741</v>
+        <v>7176723</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125760074</v>
+        <v>125760053</v>
       </c>
       <c r="B66" t="n">
-        <v>91530</v>
+        <v>91236</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6930,21 +6930,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>774149</v>
+        <v>774161</v>
       </c>
       <c r="R66" t="n">
-        <v>7176723</v>
+        <v>7176741</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7116,7 +7116,7 @@
         <v>125760103</v>
       </c>
       <c r="B68" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91641</v>
+        <v>91643</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125760092</v>
+        <v>125760046</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>79005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>773927</v>
+        <v>773999</v>
       </c>
       <c r="R6" t="n">
-        <v>7176601</v>
+        <v>7176749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,6 +1146,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1164,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125760093</v>
+        <v>125760092</v>
       </c>
       <c r="B7" t="n">
         <v>98343</v>
@@ -1199,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>773964</v>
+        <v>773927</v>
       </c>
       <c r="R7" t="n">
-        <v>7176602</v>
+        <v>7176601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125760046</v>
+        <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>79005</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>773999</v>
+        <v>773964</v>
       </c>
       <c r="R8" t="n">
-        <v>7176749</v>
+        <v>7176602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1340,7 +1341,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760090</v>
+        <v>125760071</v>
       </c>
       <c r="B9" t="n">
-        <v>98343</v>
+        <v>91690</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>773892</v>
+        <v>774022</v>
       </c>
       <c r="R9" t="n">
-        <v>7176629</v>
+        <v>7176810</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760094</v>
+        <v>125760090</v>
       </c>
       <c r="B10" t="n">
         <v>98343</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774050</v>
+        <v>773892</v>
       </c>
       <c r="R10" t="n">
-        <v>7176592</v>
+        <v>7176629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760071</v>
+        <v>125760094</v>
       </c>
       <c r="B11" t="n">
-        <v>91690</v>
+        <v>98343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774022</v>
+        <v>774050</v>
       </c>
       <c r="R11" t="n">
-        <v>7176810</v>
+        <v>7176592</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760069</v>
+        <v>125760119</v>
       </c>
       <c r="B13" t="n">
-        <v>57649</v>
+        <v>80111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>774048</v>
+        <v>773979</v>
       </c>
       <c r="R13" t="n">
-        <v>7176608</v>
+        <v>7176725</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125760070</v>
+        <v>125760069</v>
       </c>
       <c r="B14" t="n">
         <v>57649</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>774000</v>
+        <v>774048</v>
       </c>
       <c r="R14" t="n">
-        <v>7176761</v>
+        <v>7176608</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125760106</v>
+        <v>125760070</v>
       </c>
       <c r="B15" t="n">
-        <v>98343</v>
+        <v>57649</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>773963</v>
+        <v>774000</v>
       </c>
       <c r="R15" t="n">
-        <v>7176727</v>
+        <v>7176761</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125760119</v>
+        <v>125760106</v>
       </c>
       <c r="B16" t="n">
-        <v>80111</v>
+        <v>98343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>773979</v>
+        <v>773963</v>
       </c>
       <c r="R16" t="n">
-        <v>7176725</v>
+        <v>7176727</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -4269,32 +4269,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125760077</v>
+        <v>125760091</v>
       </c>
       <c r="B39" t="n">
-        <v>91532</v>
+        <v>98343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>773963</v>
+        <v>773895</v>
       </c>
       <c r="R39" t="n">
-        <v>7176727</v>
+        <v>7176617</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125760091</v>
+        <v>125760077</v>
       </c>
       <c r="B40" t="n">
-        <v>98343</v>
+        <v>91532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>773895</v>
+        <v>773963</v>
       </c>
       <c r="R40" t="n">
-        <v>7176617</v>
+        <v>7176727</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760116</v>
+        <v>125760095</v>
       </c>
       <c r="B48" t="n">
-        <v>98260</v>
+        <v>98343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774119</v>
+        <v>774109</v>
       </c>
       <c r="R48" t="n">
-        <v>7176822</v>
+        <v>7176695</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760095</v>
+        <v>125760100</v>
       </c>
       <c r="B49" t="n">
         <v>98343</v>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774109</v>
+        <v>774165</v>
       </c>
       <c r="R49" t="n">
-        <v>7176695</v>
+        <v>7176738</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,7 +5357,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760100</v>
+        <v>125760096</v>
       </c>
       <c r="B50" t="n">
         <v>98343</v>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774165</v>
+        <v>774131</v>
       </c>
       <c r="R50" t="n">
-        <v>7176738</v>
+        <v>7176720</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760096</v>
+        <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98343</v>
+        <v>98260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774131</v>
+        <v>774119</v>
       </c>
       <c r="R51" t="n">
-        <v>7176720</v>
+        <v>7176822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125760099</v>
+        <v>125760062</v>
       </c>
       <c r="B53" t="n">
-        <v>98343</v>
+        <v>57812</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>774146</v>
+        <v>774110</v>
       </c>
       <c r="R53" t="n">
-        <v>7176735</v>
+        <v>7176824</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,32 +5745,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125760062</v>
+        <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>57812</v>
+        <v>98343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>774110</v>
+        <v>774146</v>
       </c>
       <c r="R54" t="n">
-        <v>7176824</v>
+        <v>7176735</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125760063</v>
+        <v>125760108</v>
       </c>
       <c r="B62" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>774078</v>
+        <v>774201</v>
       </c>
       <c r="R62" t="n">
-        <v>7176829</v>
+        <v>7176809</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125760108</v>
+        <v>125760063</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>774201</v>
+        <v>774078</v>
       </c>
       <c r="R64" t="n">
-        <v>7176809</v>
+        <v>7176829</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125760112</v>
+        <v>125760088</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>91825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774025</v>
+        <v>774000</v>
       </c>
       <c r="R2" t="n">
-        <v>7176810</v>
+        <v>7176753</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,48 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125760088</v>
+        <v>125760051</v>
       </c>
       <c r="B3" t="n">
-        <v>91823</v>
+        <v>91238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774000</v>
+        <v>773924</v>
       </c>
       <c r="R3" t="n">
-        <v>7176753</v>
+        <v>7176602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125760051</v>
+        <v>125760112</v>
       </c>
       <c r="B4" t="n">
-        <v>91236</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>773924</v>
+        <v>774025</v>
       </c>
       <c r="R4" t="n">
-        <v>7176602</v>
+        <v>7176810</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125760046</v>
+        <v>125760092</v>
       </c>
       <c r="B6" t="n">
-        <v>79005</v>
+        <v>98345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>773999</v>
+        <v>773927</v>
       </c>
       <c r="R6" t="n">
-        <v>7176749</v>
+        <v>7176601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,7 +1146,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1165,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125760092</v>
+        <v>125760093</v>
       </c>
       <c r="B7" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>773927</v>
+        <v>773964</v>
       </c>
       <c r="R7" t="n">
-        <v>7176601</v>
+        <v>7176602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1261,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125760093</v>
+        <v>125760046</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>79005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>773964</v>
+        <v>773999</v>
       </c>
       <c r="R8" t="n">
-        <v>7176602</v>
+        <v>7176749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,6 +1340,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760071</v>
+        <v>125760090</v>
       </c>
       <c r="B9" t="n">
-        <v>91690</v>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774022</v>
+        <v>773892</v>
       </c>
       <c r="R9" t="n">
-        <v>7176810</v>
+        <v>7176629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760090</v>
+        <v>125760094</v>
       </c>
       <c r="B10" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>773892</v>
+        <v>774050</v>
       </c>
       <c r="R10" t="n">
-        <v>7176629</v>
+        <v>7176592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760094</v>
+        <v>125760071</v>
       </c>
       <c r="B11" t="n">
-        <v>98343</v>
+        <v>91692</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774050</v>
+        <v>774022</v>
       </c>
       <c r="R11" t="n">
-        <v>7176592</v>
+        <v>7176810</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125760056</v>
+        <v>125760069</v>
       </c>
       <c r="B12" t="n">
-        <v>91236</v>
+        <v>57649</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>773968</v>
+        <v>774048</v>
       </c>
       <c r="R12" t="n">
-        <v>7176780</v>
+        <v>7176608</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760119</v>
+        <v>125760070</v>
       </c>
       <c r="B13" t="n">
-        <v>80111</v>
+        <v>57649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>773979</v>
+        <v>774000</v>
       </c>
       <c r="R13" t="n">
-        <v>7176725</v>
+        <v>7176761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125760069</v>
+        <v>125760056</v>
       </c>
       <c r="B14" t="n">
-        <v>57649</v>
+        <v>91238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>774048</v>
+        <v>773968</v>
       </c>
       <c r="R14" t="n">
-        <v>7176608</v>
+        <v>7176780</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125760070</v>
+        <v>125760119</v>
       </c>
       <c r="B15" t="n">
-        <v>57649</v>
+        <v>80111</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774000</v>
+        <v>773979</v>
       </c>
       <c r="R15" t="n">
-        <v>7176761</v>
+        <v>7176725</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>125760106</v>
       </c>
       <c r="B16" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125760089</v>
+        <v>125760114</v>
       </c>
       <c r="B17" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>773952</v>
+        <v>773976</v>
       </c>
       <c r="R17" t="n">
-        <v>7176706</v>
+        <v>7176802</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125760114</v>
+        <v>125760084</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>773976</v>
+        <v>773979</v>
       </c>
       <c r="R18" t="n">
-        <v>7176802</v>
+        <v>7176725</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125760084</v>
+        <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>773979</v>
+        <v>773952</v>
       </c>
       <c r="R19" t="n">
-        <v>7176725</v>
+        <v>7176706</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125760081</v>
+        <v>125760058</v>
       </c>
       <c r="B20" t="n">
-        <v>80104</v>
+        <v>91238</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>773937</v>
+        <v>774022</v>
       </c>
       <c r="R20" t="n">
-        <v>7176636</v>
+        <v>7176810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125760058</v>
+        <v>125760081</v>
       </c>
       <c r="B21" t="n">
-        <v>91236</v>
+        <v>80104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>774022</v>
+        <v>773937</v>
       </c>
       <c r="R21" t="n">
-        <v>7176810</v>
+        <v>7176636</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125760066</v>
+        <v>125760082</v>
       </c>
       <c r="B22" t="n">
-        <v>91186</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>774006</v>
+        <v>773931</v>
       </c>
       <c r="R22" t="n">
-        <v>7176718</v>
+        <v>7176699</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125760057</v>
+        <v>125760110</v>
       </c>
       <c r="B23" t="n">
-        <v>91236</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>774006</v>
+        <v>774041</v>
       </c>
       <c r="R23" t="n">
-        <v>7176806</v>
+        <v>7176829</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125760110</v>
+        <v>125760066</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>91188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>774041</v>
+        <v>774006</v>
       </c>
       <c r="R24" t="n">
-        <v>7176829</v>
+        <v>7176718</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125760082</v>
+        <v>125760057</v>
       </c>
       <c r="B25" t="n">
-        <v>80076</v>
+        <v>91238</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>773931</v>
+        <v>774006</v>
       </c>
       <c r="R25" t="n">
-        <v>7176699</v>
+        <v>7176806</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125760059</v>
+        <v>125760045</v>
       </c>
       <c r="B27" t="n">
-        <v>91933</v>
+        <v>79005</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>774009</v>
+        <v>773995</v>
       </c>
       <c r="R27" t="n">
-        <v>7176814</v>
+        <v>7176808</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125760045</v>
+        <v>125760059</v>
       </c>
       <c r="B28" t="n">
-        <v>79005</v>
+        <v>91935</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>773995</v>
+        <v>774009</v>
       </c>
       <c r="R28" t="n">
-        <v>7176808</v>
+        <v>7176814</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3302,7 +3302,7 @@
         <v>125760073</v>
       </c>
       <c r="B29" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>125760067</v>
       </c>
       <c r="B31" t="n">
-        <v>91186</v>
+        <v>91188</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>125760050</v>
       </c>
       <c r="B32" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125760048</v>
+        <v>125760044</v>
       </c>
       <c r="B33" t="n">
-        <v>91201</v>
+        <v>79005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>774008</v>
+        <v>774005</v>
       </c>
       <c r="R33" t="n">
-        <v>7176756</v>
+        <v>7176711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125760044</v>
+        <v>125760055</v>
       </c>
       <c r="B34" t="n">
-        <v>79005</v>
+        <v>91238</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>774005</v>
+        <v>773997</v>
       </c>
       <c r="R34" t="n">
-        <v>7176711</v>
+        <v>7176755</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3881,32 +3881,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125760055</v>
+        <v>125760048</v>
       </c>
       <c r="B35" t="n">
-        <v>91236</v>
+        <v>91203</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>773997</v>
+        <v>774008</v>
       </c>
       <c r="R35" t="n">
-        <v>7176755</v>
+        <v>7176756</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3981,7 +3981,7 @@
         <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,32 +4269,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125760091</v>
+        <v>125760077</v>
       </c>
       <c r="B39" t="n">
-        <v>98343</v>
+        <v>91534</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>773895</v>
+        <v>773963</v>
       </c>
       <c r="R39" t="n">
-        <v>7176617</v>
+        <v>7176727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125760077</v>
+        <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>91532</v>
+        <v>98345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>773963</v>
+        <v>773895</v>
       </c>
       <c r="R40" t="n">
-        <v>7176727</v>
+        <v>7176617</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125760064</v>
+        <v>125760105</v>
       </c>
       <c r="B42" t="n">
-        <v>57812</v>
+        <v>98345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>773973</v>
+        <v>773966</v>
       </c>
       <c r="R42" t="n">
-        <v>7176728</v>
+        <v>7176724</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125760105</v>
+        <v>125760064</v>
       </c>
       <c r="B43" t="n">
-        <v>98343</v>
+        <v>57812</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>773966</v>
+        <v>773973</v>
       </c>
       <c r="R43" t="n">
-        <v>7176724</v>
+        <v>7176728</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
         <v>125760118</v>
       </c>
       <c r="B46" t="n">
-        <v>88645</v>
+        <v>88647</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760095</v>
+        <v>125760116</v>
       </c>
       <c r="B48" t="n">
-        <v>98343</v>
+        <v>98262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774109</v>
+        <v>774119</v>
       </c>
       <c r="R48" t="n">
-        <v>7176695</v>
+        <v>7176822</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760100</v>
+        <v>125760096</v>
       </c>
       <c r="B49" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774165</v>
+        <v>774131</v>
       </c>
       <c r="R49" t="n">
-        <v>7176738</v>
+        <v>7176720</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,10 +5357,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760096</v>
+        <v>125760100</v>
       </c>
       <c r="B50" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774131</v>
+        <v>774165</v>
       </c>
       <c r="R50" t="n">
-        <v>7176720</v>
+        <v>7176738</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760116</v>
+        <v>125760095</v>
       </c>
       <c r="B51" t="n">
-        <v>98260</v>
+        <v>98345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774119</v>
+        <v>774109</v>
       </c>
       <c r="R51" t="n">
-        <v>7176822</v>
+        <v>7176695</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5554,7 +5554,7 @@
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125760052</v>
+        <v>125760115</v>
       </c>
       <c r="B55" t="n">
-        <v>91236</v>
+        <v>57652</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>774143</v>
+        <v>774095</v>
       </c>
       <c r="R55" t="n">
-        <v>7176723</v>
+        <v>7176826</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5913,6 +5913,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5939,10 +5944,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125760115</v>
+        <v>125760052</v>
       </c>
       <c r="B56" t="n">
-        <v>57652</v>
+        <v>91238</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5950,21 +5955,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5974,10 +5979,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>774095</v>
+        <v>774143</v>
       </c>
       <c r="R56" t="n">
-        <v>7176826</v>
+        <v>7176723</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6010,11 +6015,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6041,10 +6041,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125760086</v>
+        <v>125760097</v>
       </c>
       <c r="B57" t="n">
-        <v>91437</v>
+        <v>98345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6052,37 +6052,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>774175</v>
+        <v>774142</v>
       </c>
       <c r="R57" t="n">
-        <v>7176775</v>
+        <v>7176720</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6123,7 +6120,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6142,10 +6138,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125760076</v>
+        <v>125760061</v>
       </c>
       <c r="B58" t="n">
-        <v>91532</v>
+        <v>57812</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6153,21 +6149,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6177,10 +6173,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>774175</v>
+        <v>774115</v>
       </c>
       <c r="R58" t="n">
-        <v>7176775</v>
+        <v>7176821</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6239,45 +6235,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760061</v>
+        <v>125760086</v>
       </c>
       <c r="B59" t="n">
-        <v>57812</v>
+        <v>91439</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>48</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>774115</v>
+        <v>774175</v>
       </c>
       <c r="R59" t="n">
-        <v>7176821</v>
+        <v>7176775</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6318,6 +6317,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6336,32 +6336,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125760097</v>
+        <v>125760076</v>
       </c>
       <c r="B60" t="n">
-        <v>98343</v>
+        <v>91534</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>774142</v>
+        <v>774175</v>
       </c>
       <c r="R60" t="n">
-        <v>7176720</v>
+        <v>7176775</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6436,7 +6436,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125760072</v>
+        <v>125760063</v>
       </c>
       <c r="B63" t="n">
-        <v>91532</v>
+        <v>57812</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>774185</v>
+        <v>774078</v>
       </c>
       <c r="R63" t="n">
-        <v>7176787</v>
+        <v>7176829</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6706,7 +6706,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6725,10 +6724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125760063</v>
+        <v>125760072</v>
       </c>
       <c r="B64" t="n">
-        <v>57812</v>
+        <v>91534</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6736,21 +6735,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6760,10 +6759,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>774078</v>
+        <v>774185</v>
       </c>
       <c r="R64" t="n">
-        <v>7176829</v>
+        <v>7176787</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,6 +6803,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125760074</v>
+        <v>125760053</v>
       </c>
       <c r="B65" t="n">
-        <v>91532</v>
+        <v>91238</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>774149</v>
+        <v>774161</v>
       </c>
       <c r="R65" t="n">
-        <v>7176723</v>
+        <v>7176741</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125760053</v>
+        <v>125760074</v>
       </c>
       <c r="B66" t="n">
-        <v>91236</v>
+        <v>91534</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6930,21 +6930,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>774161</v>
+        <v>774149</v>
       </c>
       <c r="R66" t="n">
-        <v>7176741</v>
+        <v>7176723</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7016,32 +7016,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125760109</v>
+        <v>125760103</v>
       </c>
       <c r="B67" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>774182</v>
+        <v>774172</v>
       </c>
       <c r="R67" t="n">
-        <v>7176808</v>
+        <v>7176751</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125760103</v>
+        <v>125760109</v>
       </c>
       <c r="B68" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>774172</v>
+        <v>774182</v>
       </c>
       <c r="R68" t="n">
-        <v>7176751</v>
+        <v>7176808</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -873,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125760112</v>
+        <v>125760083</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774025</v>
+        <v>774042</v>
       </c>
       <c r="R4" t="n">
-        <v>7176810</v>
+        <v>7176609</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125760083</v>
+        <v>125760112</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774042</v>
+        <v>774025</v>
       </c>
       <c r="R5" t="n">
-        <v>7176609</v>
+        <v>7176810</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125760092</v>
+        <v>125760046</v>
       </c>
       <c r="B6" t="n">
-        <v>98345</v>
+        <v>79005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>773927</v>
+        <v>773999</v>
       </c>
       <c r="R6" t="n">
-        <v>7176601</v>
+        <v>7176749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,6 +1146,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1164,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125760093</v>
+        <v>125760092</v>
       </c>
       <c r="B7" t="n">
         <v>98345</v>
@@ -1199,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>773964</v>
+        <v>773927</v>
       </c>
       <c r="R7" t="n">
-        <v>7176602</v>
+        <v>7176601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125760046</v>
+        <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>79005</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>773999</v>
+        <v>773964</v>
       </c>
       <c r="R8" t="n">
-        <v>7176749</v>
+        <v>7176602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1340,7 +1341,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760090</v>
+        <v>125760071</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>91692</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>773892</v>
+        <v>774022</v>
       </c>
       <c r="R9" t="n">
-        <v>7176629</v>
+        <v>7176810</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760094</v>
+        <v>125760090</v>
       </c>
       <c r="B10" t="n">
         <v>98345</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774050</v>
+        <v>773892</v>
       </c>
       <c r="R10" t="n">
-        <v>7176592</v>
+        <v>7176629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760071</v>
+        <v>125760094</v>
       </c>
       <c r="B11" t="n">
-        <v>91692</v>
+        <v>98345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774022</v>
+        <v>774050</v>
       </c>
       <c r="R11" t="n">
-        <v>7176810</v>
+        <v>7176592</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125760114</v>
+        <v>125760084</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>773976</v>
+        <v>773979</v>
       </c>
       <c r="R17" t="n">
-        <v>7176802</v>
+        <v>7176725</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,32 +2232,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125760084</v>
+        <v>125760089</v>
       </c>
       <c r="B18" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>773979</v>
+        <v>773952</v>
       </c>
       <c r="R18" t="n">
-        <v>7176725</v>
+        <v>7176706</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125760089</v>
+        <v>125760114</v>
       </c>
       <c r="B19" t="n">
-        <v>98345</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>773952</v>
+        <v>773976</v>
       </c>
       <c r="R19" t="n">
-        <v>7176706</v>
+        <v>7176802</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125760073</v>
+        <v>125760085</v>
       </c>
       <c r="B29" t="n">
-        <v>91534</v>
+        <v>80076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>773962</v>
+        <v>774028</v>
       </c>
       <c r="R29" t="n">
-        <v>7176754</v>
+        <v>7176813</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125760085</v>
+        <v>125760073</v>
       </c>
       <c r="B30" t="n">
-        <v>80076</v>
+        <v>91534</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>774028</v>
+        <v>773962</v>
       </c>
       <c r="R30" t="n">
-        <v>7176813</v>
+        <v>7176754</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125760105</v>
+        <v>125760064</v>
       </c>
       <c r="B42" t="n">
-        <v>98345</v>
+        <v>57812</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>773966</v>
+        <v>773973</v>
       </c>
       <c r="R42" t="n">
-        <v>7176724</v>
+        <v>7176728</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125760064</v>
+        <v>125760105</v>
       </c>
       <c r="B43" t="n">
-        <v>57812</v>
+        <v>98345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>773973</v>
+        <v>773966</v>
       </c>
       <c r="R43" t="n">
-        <v>7176728</v>
+        <v>7176724</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125760118</v>
+        <v>125760117</v>
       </c>
       <c r="B46" t="n">
-        <v>88647</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4972,34 +4972,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>774109</v>
+        <v>774183</v>
       </c>
       <c r="R46" t="n">
-        <v>7176799</v>
+        <v>7176785</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5040,6 +5047,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5058,10 +5066,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125760117</v>
+        <v>125760118</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>88647</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5069,41 +5077,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>774183</v>
+        <v>774109</v>
       </c>
       <c r="R47" t="n">
-        <v>7176785</v>
+        <v>7176799</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5144,7 +5145,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760116</v>
+        <v>125760096</v>
       </c>
       <c r="B48" t="n">
-        <v>98262</v>
+        <v>98345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774119</v>
+        <v>774131</v>
       </c>
       <c r="R48" t="n">
-        <v>7176822</v>
+        <v>7176720</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760096</v>
+        <v>125760100</v>
       </c>
       <c r="B49" t="n">
         <v>98345</v>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774131</v>
+        <v>774165</v>
       </c>
       <c r="R49" t="n">
-        <v>7176720</v>
+        <v>7176738</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,7 +5357,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760100</v>
+        <v>125760095</v>
       </c>
       <c r="B50" t="n">
         <v>98345</v>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774165</v>
+        <v>774109</v>
       </c>
       <c r="R50" t="n">
-        <v>7176738</v>
+        <v>7176695</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760095</v>
+        <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98345</v>
+        <v>98262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774109</v>
+        <v>774119</v>
       </c>
       <c r="R51" t="n">
-        <v>7176695</v>
+        <v>7176822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125760088</v>
+        <v>125760083</v>
       </c>
       <c r="B2" t="n">
-        <v>91825</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1179</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774000</v>
+        <v>774042</v>
       </c>
       <c r="R2" t="n">
-        <v>7176753</v>
+        <v>7176609</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125760051</v>
+        <v>125760112</v>
       </c>
       <c r="B3" t="n">
-        <v>91238</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>773924</v>
+        <v>774025</v>
       </c>
       <c r="R3" t="n">
-        <v>7176602</v>
+        <v>7176810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,45 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125760083</v>
+        <v>125760088</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>91829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774042</v>
+        <v>774000</v>
       </c>
       <c r="R4" t="n">
-        <v>7176609</v>
+        <v>7176753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125760112</v>
+        <v>125760051</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>91242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774025</v>
+        <v>773924</v>
       </c>
       <c r="R5" t="n">
-        <v>7176810</v>
+        <v>7176602</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125760046</v>
+        <v>125760092</v>
       </c>
       <c r="B6" t="n">
-        <v>79005</v>
+        <v>98349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>773999</v>
+        <v>773927</v>
       </c>
       <c r="R6" t="n">
-        <v>7176749</v>
+        <v>7176601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,7 +1146,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1165,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125760092</v>
+        <v>125760093</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>773927</v>
+        <v>773964</v>
       </c>
       <c r="R7" t="n">
-        <v>7176601</v>
+        <v>7176602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1261,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125760093</v>
+        <v>125760046</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>79009</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>773964</v>
+        <v>773999</v>
       </c>
       <c r="R8" t="n">
-        <v>7176602</v>
+        <v>7176749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,6 +1340,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>125760071</v>
       </c>
       <c r="B9" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125760090</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125760094</v>
       </c>
       <c r="B11" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125760069</v>
+        <v>125760056</v>
       </c>
       <c r="B12" t="n">
-        <v>57649</v>
+        <v>91242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>774048</v>
+        <v>773968</v>
       </c>
       <c r="R12" t="n">
-        <v>7176608</v>
+        <v>7176780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,7 +1750,7 @@
         <v>125760070</v>
       </c>
       <c r="B13" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125760056</v>
+        <v>125760069</v>
       </c>
       <c r="B14" t="n">
-        <v>91238</v>
+        <v>57653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>773968</v>
+        <v>774048</v>
       </c>
       <c r="R14" t="n">
-        <v>7176780</v>
+        <v>7176608</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125760119</v>
+        <v>125760106</v>
       </c>
       <c r="B15" t="n">
-        <v>80111</v>
+        <v>98349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>773979</v>
+        <v>773963</v>
       </c>
       <c r="R15" t="n">
-        <v>7176725</v>
+        <v>7176727</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125760106</v>
+        <v>125760119</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>80115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>773963</v>
+        <v>773979</v>
       </c>
       <c r="R16" t="n">
-        <v>7176727</v>
+        <v>7176725</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125760084</v>
+        <v>125760114</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>773979</v>
+        <v>773976</v>
       </c>
       <c r="R17" t="n">
-        <v>7176725</v>
+        <v>7176802</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,32 +2232,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125760089</v>
+        <v>125760084</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>773952</v>
+        <v>773979</v>
       </c>
       <c r="R18" t="n">
-        <v>7176706</v>
+        <v>7176725</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125760114</v>
+        <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>773976</v>
+        <v>773952</v>
       </c>
       <c r="R19" t="n">
-        <v>7176802</v>
+        <v>7176706</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
         <v>125760058</v>
       </c>
       <c r="B20" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>125760081</v>
       </c>
       <c r="B21" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125760082</v>
+        <v>125760057</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>91242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>773931</v>
+        <v>774006</v>
       </c>
       <c r="R22" t="n">
-        <v>7176699</v>
+        <v>7176806</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125760110</v>
+        <v>125760082</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>774041</v>
+        <v>773931</v>
       </c>
       <c r="R23" t="n">
-        <v>7176829</v>
+        <v>7176699</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
         <v>125760066</v>
       </c>
       <c r="B24" t="n">
-        <v>91188</v>
+        <v>91192</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125760057</v>
+        <v>125760110</v>
       </c>
       <c r="B25" t="n">
-        <v>91238</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>774006</v>
+        <v>774041</v>
       </c>
       <c r="R25" t="n">
-        <v>7176806</v>
+        <v>7176829</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3011,7 +3011,7 @@
         <v>125760111</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125760045</v>
       </c>
       <c r="B27" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>125760059</v>
       </c>
       <c r="B28" t="n">
-        <v>91935</v>
+        <v>91939</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>125760085</v>
       </c>
       <c r="B29" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125760073</v>
       </c>
       <c r="B30" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125760067</v>
+        <v>125760050</v>
       </c>
       <c r="B31" t="n">
-        <v>91188</v>
+        <v>91242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>774003</v>
+        <v>773962</v>
       </c>
       <c r="R31" t="n">
-        <v>7176722</v>
+        <v>7176754</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125760050</v>
+        <v>125760067</v>
       </c>
       <c r="B32" t="n">
-        <v>91238</v>
+        <v>91192</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>773962</v>
+        <v>774003</v>
       </c>
       <c r="R32" t="n">
-        <v>7176754</v>
+        <v>7176722</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125760044</v>
+        <v>125760055</v>
       </c>
       <c r="B33" t="n">
-        <v>79005</v>
+        <v>91242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3698,21 +3698,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>774005</v>
+        <v>773997</v>
       </c>
       <c r="R33" t="n">
-        <v>7176711</v>
+        <v>7176755</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125760055</v>
+        <v>125760044</v>
       </c>
       <c r="B34" t="n">
-        <v>91238</v>
+        <v>79009</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>773997</v>
+        <v>774005</v>
       </c>
       <c r="R34" t="n">
-        <v>7176755</v>
+        <v>7176711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3884,7 +3884,7 @@
         <v>125760048</v>
       </c>
       <c r="B35" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125760049</v>
+        <v>125760113</v>
       </c>
       <c r="B36" t="n">
-        <v>91596</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>773997</v>
+        <v>774009</v>
       </c>
       <c r="R36" t="n">
-        <v>7176755</v>
+        <v>7176817</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125760113</v>
+        <v>125760049</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>91600</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>774009</v>
+        <v>773997</v>
       </c>
       <c r="R37" t="n">
-        <v>7176817</v>
+        <v>7176755</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4175,7 +4175,7 @@
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>125760077</v>
       </c>
       <c r="B39" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>125760064</v>
       </c>
       <c r="B42" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>125760105</v>
       </c>
       <c r="B43" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>125760065</v>
       </c>
       <c r="B44" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>125760068</v>
       </c>
       <c r="B45" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>125760117</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>125760118</v>
       </c>
       <c r="B47" t="n">
-        <v>88647</v>
+        <v>88651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760096</v>
+        <v>125760116</v>
       </c>
       <c r="B48" t="n">
-        <v>98345</v>
+        <v>98266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774131</v>
+        <v>774119</v>
       </c>
       <c r="R48" t="n">
-        <v>7176720</v>
+        <v>7176822</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760100</v>
+        <v>125760096</v>
       </c>
       <c r="B49" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774165</v>
+        <v>774131</v>
       </c>
       <c r="R49" t="n">
-        <v>7176738</v>
+        <v>7176720</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,10 +5357,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760095</v>
+        <v>125760100</v>
       </c>
       <c r="B50" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774109</v>
+        <v>774165</v>
       </c>
       <c r="R50" t="n">
-        <v>7176695</v>
+        <v>7176738</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760116</v>
+        <v>125760095</v>
       </c>
       <c r="B51" t="n">
-        <v>98262</v>
+        <v>98349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774119</v>
+        <v>774109</v>
       </c>
       <c r="R51" t="n">
-        <v>7176822</v>
+        <v>7176695</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5554,7 +5554,7 @@
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>125760062</v>
       </c>
       <c r="B53" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125760115</v>
+        <v>125760052</v>
       </c>
       <c r="B55" t="n">
-        <v>57652</v>
+        <v>91242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>774095</v>
+        <v>774143</v>
       </c>
       <c r="R55" t="n">
-        <v>7176826</v>
+        <v>7176723</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5913,11 +5913,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5944,10 +5939,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125760052</v>
+        <v>125760115</v>
       </c>
       <c r="B56" t="n">
-        <v>91238</v>
+        <v>57656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5955,21 +5950,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5979,10 +5974,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>774143</v>
+        <v>774095</v>
       </c>
       <c r="R56" t="n">
-        <v>7176723</v>
+        <v>7176826</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6015,6 +6010,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6041,10 +6041,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125760097</v>
+        <v>125760086</v>
       </c>
       <c r="B57" t="n">
-        <v>98345</v>
+        <v>91443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6052,34 +6052,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>774142</v>
+        <v>774175</v>
       </c>
       <c r="R57" t="n">
-        <v>7176720</v>
+        <v>7176775</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6120,6 +6123,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6141,7 +6145,7 @@
         <v>125760061</v>
       </c>
       <c r="B58" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6235,38 +6239,35 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760086</v>
+        <v>125760076</v>
       </c>
       <c r="B59" t="n">
-        <v>91439</v>
+        <v>91538</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
@@ -6317,7 +6318,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6336,32 +6336,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125760076</v>
+        <v>125760097</v>
       </c>
       <c r="B60" t="n">
-        <v>91534</v>
+        <v>98349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>774175</v>
+        <v>774142</v>
       </c>
       <c r="R60" t="n">
-        <v>7176775</v>
+        <v>7176720</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6436,7 +6436,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125760108</v>
+        <v>125760063</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>57816</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>774201</v>
+        <v>774078</v>
       </c>
       <c r="R62" t="n">
-        <v>7176809</v>
+        <v>7176829</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125760063</v>
+        <v>125760108</v>
       </c>
       <c r="B63" t="n">
-        <v>57812</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>774078</v>
+        <v>774201</v>
       </c>
       <c r="R63" t="n">
-        <v>7176829</v>
+        <v>7176809</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6727,7 +6727,7 @@
         <v>125760072</v>
       </c>
       <c r="B64" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>125760053</v>
       </c>
       <c r="B65" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>125760074</v>
       </c>
       <c r="B66" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7016,32 +7016,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125760103</v>
+        <v>125760109</v>
       </c>
       <c r="B67" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>774172</v>
+        <v>774182</v>
       </c>
       <c r="R67" t="n">
-        <v>7176751</v>
+        <v>7176808</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125760109</v>
+        <v>125760103</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>774182</v>
+        <v>774172</v>
       </c>
       <c r="R68" t="n">
-        <v>7176808</v>
+        <v>7176751</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>125760080</v>
       </c>
       <c r="B74" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91645</v>
+        <v>91649</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125760056</v>
+        <v>125760106</v>
       </c>
       <c r="B12" t="n">
-        <v>91242</v>
+        <v>98349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>773968</v>
+        <v>773963</v>
       </c>
       <c r="R12" t="n">
-        <v>7176780</v>
+        <v>7176727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760070</v>
+        <v>125760056</v>
       </c>
       <c r="B13" t="n">
-        <v>57653</v>
+        <v>91242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>774000</v>
+        <v>773968</v>
       </c>
       <c r="R13" t="n">
-        <v>7176761</v>
+        <v>7176780</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125760069</v>
+        <v>125760119</v>
       </c>
       <c r="B14" t="n">
-        <v>57653</v>
+        <v>80115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>774048</v>
+        <v>773979</v>
       </c>
       <c r="R14" t="n">
-        <v>7176608</v>
+        <v>7176725</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125760106</v>
+        <v>125760070</v>
       </c>
       <c r="B15" t="n">
-        <v>98349</v>
+        <v>57653</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>773963</v>
+        <v>774000</v>
       </c>
       <c r="R15" t="n">
-        <v>7176727</v>
+        <v>7176761</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125760119</v>
+        <v>125760069</v>
       </c>
       <c r="B16" t="n">
-        <v>80115</v>
+        <v>57653</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>773979</v>
+        <v>774048</v>
       </c>
       <c r="R16" t="n">
-        <v>7176725</v>
+        <v>7176608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125760082</v>
+        <v>125760110</v>
       </c>
       <c r="B23" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>773931</v>
+        <v>774041</v>
       </c>
       <c r="R23" t="n">
-        <v>7176699</v>
+        <v>7176829</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125760066</v>
+        <v>125760082</v>
       </c>
       <c r="B24" t="n">
-        <v>91192</v>
+        <v>80080</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>774006</v>
+        <v>773931</v>
       </c>
       <c r="R24" t="n">
-        <v>7176718</v>
+        <v>7176699</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125760110</v>
+        <v>125760066</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>91192</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>774041</v>
+        <v>774006</v>
       </c>
       <c r="R25" t="n">
-        <v>7176829</v>
+        <v>7176718</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125760113</v>
+        <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>91600</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>774009</v>
+        <v>773997</v>
       </c>
       <c r="R36" t="n">
-        <v>7176817</v>
+        <v>7176755</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125760049</v>
+        <v>125760113</v>
       </c>
       <c r="B37" t="n">
-        <v>91600</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>773997</v>
+        <v>774009</v>
       </c>
       <c r="R37" t="n">
-        <v>7176755</v>
+        <v>7176817</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125760083</v>
+        <v>125760112</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774042</v>
+        <v>774025</v>
       </c>
       <c r="R2" t="n">
-        <v>7176609</v>
+        <v>7176810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125760112</v>
+        <v>125760083</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774025</v>
+        <v>774042</v>
       </c>
       <c r="R3" t="n">
-        <v>7176810</v>
+        <v>7176609</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125760092</v>
+        <v>125760046</v>
       </c>
       <c r="B6" t="n">
-        <v>98349</v>
+        <v>79009</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>773927</v>
+        <v>773999</v>
       </c>
       <c r="R6" t="n">
-        <v>7176601</v>
+        <v>7176749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,6 +1146,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1164,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125760093</v>
+        <v>125760092</v>
       </c>
       <c r="B7" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>773964</v>
+        <v>773927</v>
       </c>
       <c r="R7" t="n">
-        <v>7176602</v>
+        <v>7176601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125760046</v>
+        <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>79009</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>773999</v>
+        <v>773964</v>
       </c>
       <c r="R8" t="n">
-        <v>7176749</v>
+        <v>7176602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1340,7 +1341,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>125760090</v>
       </c>
       <c r="B10" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125760094</v>
       </c>
       <c r="B11" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125760106</v>
       </c>
       <c r="B12" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125760070</v>
+        <v>125760069</v>
       </c>
       <c r="B15" t="n">
         <v>57653</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774000</v>
+        <v>774048</v>
       </c>
       <c r="R15" t="n">
-        <v>7176761</v>
+        <v>7176608</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125760069</v>
+        <v>125760070</v>
       </c>
       <c r="B16" t="n">
         <v>57653</v>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>774048</v>
+        <v>774000</v>
       </c>
       <c r="R16" t="n">
-        <v>7176608</v>
+        <v>7176761</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
         <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125760057</v>
+        <v>125760110</v>
       </c>
       <c r="B22" t="n">
-        <v>91242</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>774006</v>
+        <v>774041</v>
       </c>
       <c r="R22" t="n">
-        <v>7176806</v>
+        <v>7176829</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125760110</v>
+        <v>125760082</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>774041</v>
+        <v>773931</v>
       </c>
       <c r="R23" t="n">
-        <v>7176829</v>
+        <v>7176699</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125760082</v>
+        <v>125760066</v>
       </c>
       <c r="B24" t="n">
-        <v>80080</v>
+        <v>91192</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>773931</v>
+        <v>774006</v>
       </c>
       <c r="R24" t="n">
-        <v>7176699</v>
+        <v>7176718</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125760066</v>
+        <v>125760057</v>
       </c>
       <c r="B25" t="n">
-        <v>91192</v>
+        <v>91242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
         <v>774006</v>
       </c>
       <c r="R25" t="n">
-        <v>7176718</v>
+        <v>7176806</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125760045</v>
+        <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>79009</v>
+        <v>91939</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>773995</v>
+        <v>774009</v>
       </c>
       <c r="R27" t="n">
-        <v>7176808</v>
+        <v>7176814</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125760059</v>
+        <v>125760045</v>
       </c>
       <c r="B28" t="n">
-        <v>91939</v>
+        <v>79009</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>774009</v>
+        <v>773995</v>
       </c>
       <c r="R28" t="n">
-        <v>7176814</v>
+        <v>7176808</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125760085</v>
+        <v>125760073</v>
       </c>
       <c r="B29" t="n">
-        <v>80080</v>
+        <v>91538</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>774028</v>
+        <v>773962</v>
       </c>
       <c r="R29" t="n">
-        <v>7176813</v>
+        <v>7176754</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125760073</v>
+        <v>125760085</v>
       </c>
       <c r="B30" t="n">
-        <v>91538</v>
+        <v>80080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>773962</v>
+        <v>774028</v>
       </c>
       <c r="R30" t="n">
-        <v>7176754</v>
+        <v>7176813</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125760050</v>
+        <v>125760067</v>
       </c>
       <c r="B31" t="n">
-        <v>91242</v>
+        <v>91192</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>773962</v>
+        <v>774003</v>
       </c>
       <c r="R31" t="n">
-        <v>7176754</v>
+        <v>7176722</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125760067</v>
+        <v>125760050</v>
       </c>
       <c r="B32" t="n">
-        <v>91192</v>
+        <v>91242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>774003</v>
+        <v>773962</v>
       </c>
       <c r="R32" t="n">
-        <v>7176722</v>
+        <v>7176754</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125760055</v>
+        <v>125760044</v>
       </c>
       <c r="B33" t="n">
-        <v>91242</v>
+        <v>79009</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3698,21 +3698,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>773997</v>
+        <v>774005</v>
       </c>
       <c r="R33" t="n">
-        <v>7176755</v>
+        <v>7176711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125760044</v>
+        <v>125760055</v>
       </c>
       <c r="B34" t="n">
-        <v>79009</v>
+        <v>91242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>774005</v>
+        <v>773997</v>
       </c>
       <c r="R34" t="n">
-        <v>7176711</v>
+        <v>7176755</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4369,7 +4369,7 @@
         <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>125760105</v>
       </c>
       <c r="B43" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125760117</v>
+        <v>125760118</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>88651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4972,41 +4972,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>774183</v>
+        <v>774109</v>
       </c>
       <c r="R46" t="n">
-        <v>7176785</v>
+        <v>7176799</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5047,7 +5040,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5066,10 +5058,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125760118</v>
+        <v>125760117</v>
       </c>
       <c r="B47" t="n">
-        <v>88651</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5077,34 +5069,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>774109</v>
+        <v>774183</v>
       </c>
       <c r="R47" t="n">
-        <v>7176799</v>
+        <v>7176785</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5145,6 +5144,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760116</v>
+        <v>125760095</v>
       </c>
       <c r="B48" t="n">
-        <v>98266</v>
+        <v>98352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774119</v>
+        <v>774109</v>
       </c>
       <c r="R48" t="n">
-        <v>7176822</v>
+        <v>7176695</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760096</v>
+        <v>125760100</v>
       </c>
       <c r="B49" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774131</v>
+        <v>774165</v>
       </c>
       <c r="R49" t="n">
-        <v>7176720</v>
+        <v>7176738</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,10 +5357,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760100</v>
+        <v>125760096</v>
       </c>
       <c r="B50" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774165</v>
+        <v>774131</v>
       </c>
       <c r="R50" t="n">
-        <v>7176738</v>
+        <v>7176720</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760095</v>
+        <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98349</v>
+        <v>98269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774109</v>
+        <v>774119</v>
       </c>
       <c r="R51" t="n">
-        <v>7176695</v>
+        <v>7176822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
         <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125760061</v>
+        <v>125760076</v>
       </c>
       <c r="B58" t="n">
-        <v>57816</v>
+        <v>91538</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>774115</v>
+        <v>774175</v>
       </c>
       <c r="R58" t="n">
-        <v>7176821</v>
+        <v>7176775</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760076</v>
+        <v>125760061</v>
       </c>
       <c r="B59" t="n">
-        <v>91538</v>
+        <v>57816</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>774175</v>
+        <v>774115</v>
       </c>
       <c r="R59" t="n">
-        <v>7176775</v>
+        <v>7176821</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6339,7 +6339,7 @@
         <v>125760097</v>
       </c>
       <c r="B60" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125760063</v>
+        <v>125760108</v>
       </c>
       <c r="B62" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>774078</v>
+        <v>774201</v>
       </c>
       <c r="R62" t="n">
-        <v>7176829</v>
+        <v>7176809</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125760108</v>
+        <v>125760063</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>774201</v>
+        <v>774078</v>
       </c>
       <c r="R63" t="n">
-        <v>7176809</v>
+        <v>7176829</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7116,7 +7116,7 @@
         <v>125760103</v>
       </c>
       <c r="B68" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760071</v>
+        <v>125760090</v>
       </c>
       <c r="B9" t="n">
-        <v>91696</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774022</v>
+        <v>773892</v>
       </c>
       <c r="R9" t="n">
-        <v>7176810</v>
+        <v>7176629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760090</v>
+        <v>125760094</v>
       </c>
       <c r="B10" t="n">
         <v>98352</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>773892</v>
+        <v>774050</v>
       </c>
       <c r="R10" t="n">
-        <v>7176629</v>
+        <v>7176592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760094</v>
+        <v>125760071</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>91696</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774050</v>
+        <v>774022</v>
       </c>
       <c r="R11" t="n">
-        <v>7176592</v>
+        <v>7176810</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125760110</v>
+        <v>125760066</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>91192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>774041</v>
+        <v>774006</v>
       </c>
       <c r="R22" t="n">
-        <v>7176829</v>
+        <v>7176718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125760082</v>
+        <v>125760057</v>
       </c>
       <c r="B23" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>773931</v>
+        <v>774006</v>
       </c>
       <c r="R23" t="n">
-        <v>7176699</v>
+        <v>7176806</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125760066</v>
+        <v>125760110</v>
       </c>
       <c r="B24" t="n">
-        <v>91192</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>774006</v>
+        <v>774041</v>
       </c>
       <c r="R24" t="n">
-        <v>7176718</v>
+        <v>7176829</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125760057</v>
+        <v>125760082</v>
       </c>
       <c r="B25" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>774006</v>
+        <v>773931</v>
       </c>
       <c r="R25" t="n">
-        <v>7176806</v>
+        <v>7176699</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125760059</v>
+        <v>125760045</v>
       </c>
       <c r="B27" t="n">
-        <v>91939</v>
+        <v>79009</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>774009</v>
+        <v>773995</v>
       </c>
       <c r="R27" t="n">
-        <v>7176814</v>
+        <v>7176808</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125760045</v>
+        <v>125760059</v>
       </c>
       <c r="B28" t="n">
-        <v>79009</v>
+        <v>91939</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>773995</v>
+        <v>774009</v>
       </c>
       <c r="R28" t="n">
-        <v>7176808</v>
+        <v>7176814</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -6239,32 +6239,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760061</v>
+        <v>125760097</v>
       </c>
       <c r="B59" t="n">
-        <v>57816</v>
+        <v>98352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>774115</v>
+        <v>774142</v>
       </c>
       <c r="R59" t="n">
-        <v>7176821</v>
+        <v>7176720</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,32 +6336,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125760097</v>
+        <v>125760061</v>
       </c>
       <c r="B60" t="n">
-        <v>98352</v>
+        <v>57816</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>774142</v>
+        <v>774115</v>
       </c>
       <c r="R60" t="n">
-        <v>7176720</v>
+        <v>7176821</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125760112</v>
+        <v>125760088</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>91829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774025</v>
+        <v>774000</v>
       </c>
       <c r="R2" t="n">
-        <v>7176810</v>
+        <v>7176753</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125760083</v>
+        <v>125760051</v>
       </c>
       <c r="B3" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774042</v>
+        <v>773924</v>
       </c>
       <c r="R3" t="n">
-        <v>7176609</v>
+        <v>7176602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,48 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125760088</v>
+        <v>125760112</v>
       </c>
       <c r="B4" t="n">
-        <v>91829</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774000</v>
+        <v>774025</v>
       </c>
       <c r="R4" t="n">
-        <v>7176753</v>
+        <v>7176810</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125760051</v>
+        <v>125760083</v>
       </c>
       <c r="B5" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>773924</v>
+        <v>774042</v>
       </c>
       <c r="R5" t="n">
-        <v>7176602</v>
+        <v>7176609</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760090</v>
+        <v>125760071</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>91696</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>773892</v>
+        <v>774022</v>
       </c>
       <c r="R9" t="n">
-        <v>7176629</v>
+        <v>7176810</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760094</v>
+        <v>125760090</v>
       </c>
       <c r="B10" t="n">
         <v>98352</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774050</v>
+        <v>773892</v>
       </c>
       <c r="R10" t="n">
-        <v>7176592</v>
+        <v>7176629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760071</v>
+        <v>125760094</v>
       </c>
       <c r="B11" t="n">
-        <v>91696</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774022</v>
+        <v>774050</v>
       </c>
       <c r="R11" t="n">
-        <v>7176810</v>
+        <v>7176592</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125760106</v>
+        <v>125760056</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>91242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>773963</v>
+        <v>773968</v>
       </c>
       <c r="R12" t="n">
-        <v>7176727</v>
+        <v>7176780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125760056</v>
+        <v>125760119</v>
       </c>
       <c r="B13" t="n">
-        <v>91242</v>
+        <v>80115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>773968</v>
+        <v>773979</v>
       </c>
       <c r="R13" t="n">
-        <v>7176780</v>
+        <v>7176725</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125760119</v>
+        <v>125760106</v>
       </c>
       <c r="B14" t="n">
-        <v>80115</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>773979</v>
+        <v>773963</v>
       </c>
       <c r="R14" t="n">
-        <v>7176725</v>
+        <v>7176727</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125760045</v>
+        <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>79009</v>
+        <v>91939</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>773995</v>
+        <v>774009</v>
       </c>
       <c r="R27" t="n">
-        <v>7176808</v>
+        <v>7176814</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125760059</v>
+        <v>125760045</v>
       </c>
       <c r="B28" t="n">
-        <v>91939</v>
+        <v>79009</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>774009</v>
+        <v>773995</v>
       </c>
       <c r="R28" t="n">
-        <v>7176814</v>
+        <v>7176808</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125760044</v>
+        <v>125760048</v>
       </c>
       <c r="B33" t="n">
-        <v>79009</v>
+        <v>91207</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>774005</v>
+        <v>774008</v>
       </c>
       <c r="R33" t="n">
-        <v>7176711</v>
+        <v>7176756</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125760055</v>
+        <v>125760044</v>
       </c>
       <c r="B34" t="n">
-        <v>91242</v>
+        <v>79009</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>773997</v>
+        <v>774005</v>
       </c>
       <c r="R34" t="n">
-        <v>7176755</v>
+        <v>7176711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3881,32 +3881,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125760048</v>
+        <v>125760055</v>
       </c>
       <c r="B35" t="n">
-        <v>91207</v>
+        <v>91242</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>774008</v>
+        <v>773997</v>
       </c>
       <c r="R35" t="n">
-        <v>7176756</v>
+        <v>7176755</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125760064</v>
+        <v>125760105</v>
       </c>
       <c r="B42" t="n">
-        <v>57816</v>
+        <v>98352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>773973</v>
+        <v>773966</v>
       </c>
       <c r="R42" t="n">
-        <v>7176728</v>
+        <v>7176724</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4657,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125760105</v>
+        <v>125760064</v>
       </c>
       <c r="B43" t="n">
-        <v>98352</v>
+        <v>57816</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>773966</v>
+        <v>773973</v>
       </c>
       <c r="R43" t="n">
-        <v>7176724</v>
+        <v>7176728</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760095</v>
+        <v>125760116</v>
       </c>
       <c r="B48" t="n">
-        <v>98352</v>
+        <v>98269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774109</v>
+        <v>774119</v>
       </c>
       <c r="R48" t="n">
-        <v>7176695</v>
+        <v>7176822</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125760100</v>
+        <v>125760095</v>
       </c>
       <c r="B49" t="n">
         <v>98352</v>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>774165</v>
+        <v>774109</v>
       </c>
       <c r="R49" t="n">
-        <v>7176738</v>
+        <v>7176695</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,7 +5357,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125760096</v>
+        <v>125760100</v>
       </c>
       <c r="B50" t="n">
         <v>98352</v>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>774131</v>
+        <v>774165</v>
       </c>
       <c r="R50" t="n">
-        <v>7176720</v>
+        <v>7176738</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760116</v>
+        <v>125760096</v>
       </c>
       <c r="B51" t="n">
-        <v>98269</v>
+        <v>98352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774119</v>
+        <v>774131</v>
       </c>
       <c r="R51" t="n">
-        <v>7176822</v>
+        <v>7176720</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6239,32 +6239,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760097</v>
+        <v>125760061</v>
       </c>
       <c r="B59" t="n">
-        <v>98352</v>
+        <v>57816</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>774142</v>
+        <v>774115</v>
       </c>
       <c r="R59" t="n">
-        <v>7176720</v>
+        <v>7176821</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,32 +6336,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125760061</v>
+        <v>125760097</v>
       </c>
       <c r="B60" t="n">
-        <v>57816</v>
+        <v>98352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>774115</v>
+        <v>774142</v>
       </c>
       <c r="R60" t="n">
-        <v>7176821</v>
+        <v>7176720</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125760108</v>
+        <v>125760072</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>91538</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>774201</v>
+        <v>774185</v>
       </c>
       <c r="R62" t="n">
-        <v>7176809</v>
+        <v>7176787</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6609,6 +6609,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6627,10 +6628,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125760063</v>
+        <v>125760108</v>
       </c>
       <c r="B63" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,21 +6639,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6662,10 +6663,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>774078</v>
+        <v>774201</v>
       </c>
       <c r="R63" t="n">
-        <v>7176829</v>
+        <v>7176809</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6724,10 +6725,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125760072</v>
+        <v>125760063</v>
       </c>
       <c r="B64" t="n">
-        <v>91538</v>
+        <v>57816</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6735,21 +6736,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6759,10 +6760,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>774185</v>
+        <v>774078</v>
       </c>
       <c r="R64" t="n">
-        <v>7176787</v>
+        <v>7176829</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6803,7 +6804,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125760071</v>
+        <v>125760090</v>
       </c>
       <c r="B9" t="n">
-        <v>91696</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774022</v>
+        <v>773892</v>
       </c>
       <c r="R9" t="n">
-        <v>7176810</v>
+        <v>7176629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125760090</v>
+        <v>125760094</v>
       </c>
       <c r="B10" t="n">
         <v>98352</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>773892</v>
+        <v>774050</v>
       </c>
       <c r="R10" t="n">
-        <v>7176629</v>
+        <v>7176592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125760094</v>
+        <v>125760071</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>91696</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774050</v>
+        <v>774022</v>
       </c>
       <c r="R11" t="n">
-        <v>7176592</v>
+        <v>7176810</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125760058</v>
+        <v>125760081</v>
       </c>
       <c r="B20" t="n">
-        <v>91242</v>
+        <v>80108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>774022</v>
+        <v>773937</v>
       </c>
       <c r="R20" t="n">
-        <v>7176810</v>
+        <v>7176636</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125760081</v>
+        <v>125760058</v>
       </c>
       <c r="B21" t="n">
-        <v>80108</v>
+        <v>91242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>773937</v>
+        <v>774022</v>
       </c>
       <c r="R21" t="n">
-        <v>7176636</v>
+        <v>7176810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125760073</v>
+        <v>125760085</v>
       </c>
       <c r="B29" t="n">
-        <v>91538</v>
+        <v>80080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>773962</v>
+        <v>774028</v>
       </c>
       <c r="R29" t="n">
-        <v>7176754</v>
+        <v>7176813</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125760085</v>
+        <v>125760073</v>
       </c>
       <c r="B30" t="n">
-        <v>80080</v>
+        <v>91538</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>774028</v>
+        <v>773962</v>
       </c>
       <c r="R30" t="n">
-        <v>7176813</v>
+        <v>7176754</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125760116</v>
+        <v>125760096</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
+        <v>98352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>774119</v>
+        <v>774131</v>
       </c>
       <c r="R48" t="n">
-        <v>7176822</v>
+        <v>7176720</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125760096</v>
+        <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98352</v>
+        <v>98269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>774131</v>
+        <v>774119</v>
       </c>
       <c r="R51" t="n">
-        <v>7176720</v>
+        <v>7176822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125760052</v>
+        <v>125760115</v>
       </c>
       <c r="B55" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>774143</v>
+        <v>774095</v>
       </c>
       <c r="R55" t="n">
-        <v>7176723</v>
+        <v>7176826</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5913,6 +5913,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5939,10 +5944,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125760115</v>
+        <v>125760052</v>
       </c>
       <c r="B56" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5950,21 +5955,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5974,10 +5979,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>774095</v>
+        <v>774143</v>
       </c>
       <c r="R56" t="n">
-        <v>7176826</v>
+        <v>7176723</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6010,11 +6015,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färskt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6041,48 +6041,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125760086</v>
+        <v>125760061</v>
       </c>
       <c r="B57" t="n">
-        <v>91443</v>
+        <v>57816</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>774175</v>
+        <v>774115</v>
       </c>
       <c r="R57" t="n">
-        <v>7176775</v>
+        <v>7176821</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6123,7 +6120,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6142,32 +6138,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125760076</v>
+        <v>125760097</v>
       </c>
       <c r="B58" t="n">
-        <v>91538</v>
+        <v>98352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6177,10 +6173,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>774175</v>
+        <v>774142</v>
       </c>
       <c r="R58" t="n">
-        <v>7176775</v>
+        <v>7176720</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6239,45 +6235,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125760061</v>
+        <v>125760086</v>
       </c>
       <c r="B59" t="n">
-        <v>57816</v>
+        <v>91443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>48</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>774115</v>
+        <v>774175</v>
       </c>
       <c r="R59" t="n">
-        <v>7176821</v>
+        <v>7176775</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6318,6 +6317,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6336,32 +6336,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125760097</v>
+        <v>125760076</v>
       </c>
       <c r="B60" t="n">
-        <v>98352</v>
+        <v>91538</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>774142</v>
+        <v>774175</v>
       </c>
       <c r="R60" t="n">
-        <v>7176720</v>
+        <v>7176775</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125760053</v>
+        <v>125760074</v>
       </c>
       <c r="B65" t="n">
-        <v>91242</v>
+        <v>91538</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>774161</v>
+        <v>774149</v>
       </c>
       <c r="R65" t="n">
-        <v>7176741</v>
+        <v>7176723</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125760074</v>
+        <v>125760053</v>
       </c>
       <c r="B66" t="n">
-        <v>91538</v>
+        <v>91242</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6930,21 +6930,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>774149</v>
+        <v>774161</v>
       </c>
       <c r="R66" t="n">
-        <v>7176723</v>
+        <v>7176741</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7016,32 +7016,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125760109</v>
+        <v>125760103</v>
       </c>
       <c r="B67" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>774182</v>
+        <v>774172</v>
       </c>
       <c r="R67" t="n">
-        <v>7176808</v>
+        <v>7176751</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125760103</v>
+        <v>125760109</v>
       </c>
       <c r="B68" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>774172</v>
+        <v>774182</v>
       </c>
       <c r="R68" t="n">
-        <v>7176751</v>
+        <v>7176808</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -4854,7 +4854,7 @@
         <v>125760068</v>
       </c>
       <c r="B45" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>125760080</v>
       </c>
       <c r="B74" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91649</v>
+        <v>91652</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125760088</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,14 +772,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>125760051</v>
       </c>
       <c r="B3" t="n">
-        <v>91242</v>
+        <v>91330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,14 +873,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>125760112</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,14 +974,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>125760083</v>
       </c>
       <c r="B5" t="n">
-        <v>80080</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,14 +1075,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>125760046</v>
       </c>
       <c r="B6" t="n">
-        <v>79009</v>
+        <v>79050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,14 +1177,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>125760092</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,14 +1278,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,14 +1379,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>125760090</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,14 +1480,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>125760094</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,14 +1581,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>125760071</v>
       </c>
       <c r="B11" t="n">
-        <v>91696</v>
+        <v>91784</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,14 +1682,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>125760056</v>
       </c>
       <c r="B12" t="n">
-        <v>91242</v>
+        <v>91330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,14 +1783,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>125760119</v>
       </c>
       <c r="B13" t="n">
-        <v>80115</v>
+        <v>80156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,14 +1884,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>125760106</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,14 +1985,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>125760069</v>
       </c>
       <c r="B15" t="n">
-        <v>57653</v>
+        <v>57658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,14 +2086,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>125760070</v>
       </c>
       <c r="B16" t="n">
-        <v>57653</v>
+        <v>57658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,14 +2187,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>125760114</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,14 +2288,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>125760084</v>
       </c>
       <c r="B18" t="n">
-        <v>80080</v>
+        <v>80121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2325,14 +2389,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,14 +2490,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>125760081</v>
       </c>
       <c r="B20" t="n">
-        <v>80108</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2519,14 +2591,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>125760058</v>
       </c>
       <c r="B21" t="n">
-        <v>91242</v>
+        <v>91330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2616,14 +2692,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>125760066</v>
       </c>
       <c r="B22" t="n">
-        <v>91192</v>
+        <v>91280</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,14 +2793,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>125760057</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>91330</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2810,14 +2894,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>125760110</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2907,14 +2995,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>125760082</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>80121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3004,14 +3096,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>125760111</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3101,14 +3197,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>91939</v>
+        <v>92027</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3198,14 +3298,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>125760045</v>
       </c>
       <c r="B28" t="n">
-        <v>79009</v>
+        <v>79050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,14 +3399,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>125760085</v>
       </c>
       <c r="B29" t="n">
-        <v>80080</v>
+        <v>80121</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3392,14 +3500,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>125760073</v>
       </c>
       <c r="B30" t="n">
-        <v>91538</v>
+        <v>91626</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3489,14 +3601,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>125760067</v>
       </c>
       <c r="B31" t="n">
-        <v>91192</v>
+        <v>91280</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3586,14 +3702,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>125760050</v>
       </c>
       <c r="B32" t="n">
-        <v>91242</v>
+        <v>91330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3683,14 +3803,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>125760048</v>
       </c>
       <c r="B33" t="n">
-        <v>91207</v>
+        <v>91295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3780,14 +3904,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>125760044</v>
       </c>
       <c r="B34" t="n">
-        <v>79009</v>
+        <v>79050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3877,14 +4005,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>125760055</v>
       </c>
       <c r="B35" t="n">
-        <v>91242</v>
+        <v>91330</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3974,14 +4106,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>91600</v>
+        <v>91688</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4071,14 +4207,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>125760113</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,14 +4308,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91538</v>
+        <v>91626</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4265,14 +4409,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>125760077</v>
       </c>
       <c r="B39" t="n">
-        <v>91538</v>
+        <v>91626</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4362,14 +4510,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4459,14 +4611,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91207</v>
+        <v>91295</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4556,14 +4712,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>125760105</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4653,14 +4813,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>125760064</v>
       </c>
       <c r="B43" t="n">
-        <v>57816</v>
+        <v>57821</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4750,14 +4914,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>125760065</v>
       </c>
       <c r="B44" t="n">
-        <v>80109</v>
+        <v>80150</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4847,14 +5015,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>125760068</v>
       </c>
       <c r="B45" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,14 +5129,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>125760118</v>
       </c>
       <c r="B46" t="n">
-        <v>88651</v>
+        <v>88733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5054,14 +5230,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>125760117</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5159,14 +5339,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>125760096</v>
       </c>
       <c r="B48" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5256,14 +5440,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>125760095</v>
       </c>
       <c r="B49" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5353,14 +5541,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>125760100</v>
       </c>
       <c r="B50" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5450,14 +5642,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98269</v>
+        <v>98365</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5547,14 +5743,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91538</v>
+        <v>91626</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5644,14 +5844,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>125760062</v>
       </c>
       <c r="B53" t="n">
-        <v>57816</v>
+        <v>57821</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5741,14 +5945,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5838,14 +6046,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>125760115</v>
       </c>
       <c r="B55" t="n">
-        <v>57656</v>
+        <v>57661</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5871,6 +6083,14 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tjärnbergsheden, Vb</t>
@@ -5940,14 +6160,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>125760052</v>
       </c>
       <c r="B56" t="n">
-        <v>91242</v>
+        <v>91330</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6037,14 +6261,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>125760061</v>
       </c>
       <c r="B57" t="n">
-        <v>57816</v>
+        <v>57821</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,14 +6362,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>125760097</v>
       </c>
       <c r="B58" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6231,14 +6463,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>125760086</v>
       </c>
       <c r="B59" t="n">
-        <v>91443</v>
+        <v>91531</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6332,14 +6568,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>125760076</v>
       </c>
       <c r="B60" t="n">
-        <v>91538</v>
+        <v>91626</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6429,14 +6669,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6526,14 +6770,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>125760072</v>
       </c>
       <c r="B62" t="n">
-        <v>91538</v>
+        <v>91626</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6624,14 +6872,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>125760108</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6721,14 +6973,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>125760063</v>
       </c>
       <c r="B64" t="n">
-        <v>57816</v>
+        <v>57821</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6818,14 +7074,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>125760074</v>
       </c>
       <c r="B65" t="n">
-        <v>91538</v>
+        <v>91626</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6915,14 +7175,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>125760053</v>
       </c>
       <c r="B66" t="n">
-        <v>91242</v>
+        <v>91330</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7012,14 +7276,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>125760103</v>
       </c>
       <c r="B67" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7109,14 +7377,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY67" t="inlineStr"/>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>125760109</v>
       </c>
       <c r="B68" t="n">
-        <v>78977</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7206,14 +7478,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY68" t="inlineStr"/>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7303,14 +7579,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7400,14 +7680,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr"/>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91242</v>
+        <v>91330</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7497,14 +7781,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98352</v>
+        <v>98448</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7594,14 +7882,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91260</v>
+        <v>91348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7691,14 +7983,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>125760080</v>
       </c>
       <c r="B74" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7801,14 +8097,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr"/>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91652</v>
+        <v>91737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7897,7 +8197,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125760088</v>
       </c>
       <c r="B2" t="n">
-        <v>91917</v>
+        <v>91919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125760051</v>
       </c>
       <c r="B3" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>125760112</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>125760083</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125760046</v>
       </c>
       <c r="B6" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125760092</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>125760090</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>125760094</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>125760071</v>
       </c>
       <c r="B11" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125760056</v>
       </c>
       <c r="B12" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>125760119</v>
       </c>
       <c r="B13" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>125760106</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>125760069</v>
       </c>
       <c r="B15" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>125760070</v>
       </c>
       <c r="B16" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>125760114</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>125760084</v>
       </c>
       <c r="B18" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>125760081</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>125760058</v>
       </c>
       <c r="B21" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>125760066</v>
       </c>
       <c r="B22" t="n">
-        <v>91280</v>
+        <v>91282</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>125760057</v>
       </c>
       <c r="B23" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>125760110</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>125760082</v>
       </c>
       <c r="B25" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>125760111</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>92027</v>
+        <v>92029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>125760045</v>
       </c>
       <c r="B28" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>125760085</v>
       </c>
       <c r="B29" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>125760073</v>
       </c>
       <c r="B30" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>125760067</v>
       </c>
       <c r="B31" t="n">
-        <v>91280</v>
+        <v>91282</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>125760050</v>
       </c>
       <c r="B32" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>125760048</v>
       </c>
       <c r="B33" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>125760044</v>
       </c>
       <c r="B34" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>125760055</v>
       </c>
       <c r="B35" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>125760113</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>125760077</v>
       </c>
       <c r="B39" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125760105</v>
       </c>
       <c r="B42" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>125760064</v>
       </c>
       <c r="B43" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>125760065</v>
       </c>
       <c r="B44" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>125760068</v>
       </c>
       <c r="B45" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>125760118</v>
       </c>
       <c r="B46" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>125760117</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>125760096</v>
       </c>
       <c r="B48" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>125760095</v>
       </c>
       <c r="B49" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>125760100</v>
       </c>
       <c r="B50" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>125760062</v>
       </c>
       <c r="B53" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>125760115</v>
       </c>
       <c r="B55" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>125760052</v>
       </c>
       <c r="B56" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>125760061</v>
       </c>
       <c r="B57" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>125760097</v>
       </c>
       <c r="B58" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>125760086</v>
       </c>
       <c r="B59" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>125760076</v>
       </c>
       <c r="B60" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>125760072</v>
       </c>
       <c r="B62" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>125760108</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>125760063</v>
       </c>
       <c r="B64" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>125760074</v>
       </c>
       <c r="B65" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>125760053</v>
       </c>
       <c r="B66" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>125760103</v>
       </c>
       <c r="B67" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>125760109</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>125760080</v>
       </c>
       <c r="B74" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91737</v>
+        <v>91739</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125760088</v>
       </c>
       <c r="B2" t="n">
-        <v>91919</v>
+        <v>91925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125760051</v>
       </c>
       <c r="B3" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125760092</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>125760090</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>125760094</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>125760071</v>
       </c>
       <c r="B11" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125760056</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>125760106</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>125760058</v>
       </c>
       <c r="B21" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>125760066</v>
       </c>
       <c r="B22" t="n">
-        <v>91282</v>
+        <v>91288</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>125760057</v>
       </c>
       <c r="B23" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>92029</v>
+        <v>92035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>125760073</v>
       </c>
       <c r="B30" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>125760067</v>
       </c>
       <c r="B31" t="n">
-        <v>91282</v>
+        <v>91288</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>125760050</v>
       </c>
       <c r="B32" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>125760048</v>
       </c>
       <c r="B33" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>125760055</v>
       </c>
       <c r="B35" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>125760077</v>
       </c>
       <c r="B39" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125760105</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>125760118</v>
       </c>
       <c r="B46" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>125760096</v>
       </c>
       <c r="B48" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>125760095</v>
       </c>
       <c r="B49" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>125760100</v>
       </c>
       <c r="B50" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>125760052</v>
       </c>
       <c r="B56" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>125760097</v>
       </c>
       <c r="B58" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>125760086</v>
       </c>
       <c r="B59" t="n">
-        <v>91533</v>
+        <v>91539</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>125760076</v>
       </c>
       <c r="B60" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>125760072</v>
       </c>
       <c r="B62" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>125760074</v>
       </c>
       <c r="B65" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>125760053</v>
       </c>
       <c r="B66" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>125760103</v>
       </c>
       <c r="B67" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91739</v>
+        <v>91745</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125760088</v>
       </c>
       <c r="B2" t="n">
-        <v>91925</v>
+        <v>91928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125760051</v>
       </c>
       <c r="B3" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>125760112</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>125760083</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125760046</v>
       </c>
       <c r="B6" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125760092</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>125760090</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>125760094</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>125760071</v>
       </c>
       <c r="B11" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125760056</v>
       </c>
       <c r="B12" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>125760119</v>
       </c>
       <c r="B13" t="n">
-        <v>80158</v>
+        <v>80161</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>125760106</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>125760069</v>
       </c>
       <c r="B15" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>125760070</v>
       </c>
       <c r="B16" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>125760114</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>125760084</v>
       </c>
       <c r="B18" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>125760081</v>
       </c>
       <c r="B20" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>125760058</v>
       </c>
       <c r="B21" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>125760066</v>
       </c>
       <c r="B22" t="n">
-        <v>91288</v>
+        <v>91291</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>125760057</v>
       </c>
       <c r="B23" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>125760110</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>125760082</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>125760111</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>125760045</v>
       </c>
       <c r="B28" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>125760085</v>
       </c>
       <c r="B29" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>125760073</v>
       </c>
       <c r="B30" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>125760067</v>
       </c>
       <c r="B31" t="n">
-        <v>91288</v>
+        <v>91291</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>125760050</v>
       </c>
       <c r="B32" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>125760048</v>
       </c>
       <c r="B33" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>125760044</v>
       </c>
       <c r="B34" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>125760055</v>
       </c>
       <c r="B35" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>125760113</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>125760077</v>
       </c>
       <c r="B39" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125760105</v>
       </c>
       <c r="B42" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>125760064</v>
       </c>
       <c r="B43" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>125760065</v>
       </c>
       <c r="B44" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>125760068</v>
       </c>
       <c r="B45" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>125760118</v>
       </c>
       <c r="B46" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>125760117</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>125760096</v>
       </c>
       <c r="B48" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>125760095</v>
       </c>
       <c r="B49" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>125760100</v>
       </c>
       <c r="B50" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>125760062</v>
       </c>
       <c r="B53" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>125760115</v>
       </c>
       <c r="B55" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>125760052</v>
       </c>
       <c r="B56" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>125760061</v>
       </c>
       <c r="B57" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>125760097</v>
       </c>
       <c r="B58" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>125760086</v>
       </c>
       <c r="B59" t="n">
-        <v>91539</v>
+        <v>91542</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>125760076</v>
       </c>
       <c r="B60" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>125760072</v>
       </c>
       <c r="B62" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>125760108</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>125760063</v>
       </c>
       <c r="B64" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>125760074</v>
       </c>
       <c r="B65" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>125760053</v>
       </c>
       <c r="B66" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>125760103</v>
       </c>
       <c r="B67" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>125760109</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>125760080</v>
       </c>
       <c r="B74" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91745</v>
+        <v>91748</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 23742-2025 artfynd.xlsx
+++ b/artfynd/A 23742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125760088</v>
       </c>
       <c r="B2" t="n">
-        <v>91928</v>
+        <v>91936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125760051</v>
       </c>
       <c r="B3" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>125760112</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>125760083</v>
       </c>
       <c r="B5" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125760046</v>
       </c>
       <c r="B6" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125760092</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>125760093</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>125760090</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>125760094</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>125760071</v>
       </c>
       <c r="B11" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125760056</v>
       </c>
       <c r="B12" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>125760119</v>
       </c>
       <c r="B13" t="n">
-        <v>80161</v>
+        <v>80167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>125760106</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>125760069</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>125760070</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>125760114</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>125760084</v>
       </c>
       <c r="B18" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>125760089</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>125760081</v>
       </c>
       <c r="B20" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>125760058</v>
       </c>
       <c r="B21" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>125760066</v>
       </c>
       <c r="B22" t="n">
-        <v>91291</v>
+        <v>91299</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>125760057</v>
       </c>
       <c r="B23" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>125760110</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>125760082</v>
       </c>
       <c r="B25" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>125760111</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>125760059</v>
       </c>
       <c r="B27" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>125760045</v>
       </c>
       <c r="B28" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>125760085</v>
       </c>
       <c r="B29" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>125760073</v>
       </c>
       <c r="B30" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>125760067</v>
       </c>
       <c r="B31" t="n">
-        <v>91291</v>
+        <v>91299</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>125760050</v>
       </c>
       <c r="B32" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>125760048</v>
       </c>
       <c r="B33" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>125760044</v>
       </c>
       <c r="B34" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>125760055</v>
       </c>
       <c r="B35" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>125760049</v>
       </c>
       <c r="B36" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>125760113</v>
       </c>
       <c r="B37" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>125760079</v>
       </c>
       <c r="B38" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>125760077</v>
       </c>
       <c r="B39" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>125760091</v>
       </c>
       <c r="B40" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>125760047</v>
       </c>
       <c r="B41" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125760105</v>
       </c>
       <c r="B42" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>125760064</v>
       </c>
       <c r="B43" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>125760065</v>
       </c>
       <c r="B44" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>125760068</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>125760118</v>
       </c>
       <c r="B46" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>125760117</v>
       </c>
       <c r="B47" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>125760096</v>
       </c>
       <c r="B48" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>125760095</v>
       </c>
       <c r="B49" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>125760100</v>
       </c>
       <c r="B50" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>125760116</v>
       </c>
       <c r="B51" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>125760075</v>
       </c>
       <c r="B52" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>125760062</v>
       </c>
       <c r="B53" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>125760099</v>
       </c>
       <c r="B54" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>125760115</v>
       </c>
       <c r="B55" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>125760052</v>
       </c>
       <c r="B56" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>125760061</v>
       </c>
       <c r="B57" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>125760097</v>
       </c>
       <c r="B58" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>125760086</v>
       </c>
       <c r="B59" t="n">
-        <v>91542</v>
+        <v>91550</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>125760076</v>
       </c>
       <c r="B60" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>125760101</v>
       </c>
       <c r="B61" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>125760072</v>
       </c>
       <c r="B62" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>125760108</v>
       </c>
       <c r="B63" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>125760063</v>
       </c>
       <c r="B64" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>125760074</v>
       </c>
       <c r="B65" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>125760053</v>
       </c>
       <c r="B66" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>125760103</v>
       </c>
       <c r="B67" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>125760109</v>
       </c>
       <c r="B68" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>125760104</v>
       </c>
       <c r="B69" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>125760098</v>
       </c>
       <c r="B70" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>125760054</v>
       </c>
       <c r="B71" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>125760102</v>
       </c>
       <c r="B72" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>125760107</v>
       </c>
       <c r="B73" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>125760080</v>
       </c>
       <c r="B74" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>125760087</v>
       </c>
       <c r="B75" t="n">
-        <v>91748</v>
+        <v>91756</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
